--- a/salidas/mapas_pendientes_v6/Matriz_Pendientes_Bloques_V6_IN_Piura.xlsx
+++ b/salidas/mapas_pendientes_v6/Matriz_Pendientes_Bloques_V6_IN_Piura.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Notas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pendientes por bloque'!$A$8:$V$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pendientes por bloque'!$A$8:$W$125</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Resumen por distrito'!$A$8:$F$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V128"/>
+  <dimension ref="A1:W128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -528,9 +528,9 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -540,8 +540,9 @@
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="28" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -582,7 +583,7 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Fuente: DEM: Copernicus GLO-30 (ESA, 30 m, modelo de superficie). Bloques: catálogo V6 (datos/unidades_liberacion_areas.csv).</t>
+          <t>Fuente: DEM: Copernicus GLO-30 (ESA, 30 m, modelo de superficie). Bloques: capa Bloques V6 (datos/bloques_v6.gpkg) y catálogo V6.</t>
         </is>
       </c>
     </row>
@@ -629,70 +630,75 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
+          <t>Área polígono (ha)</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
           <t>Pend. media (%)</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Mediana (%)</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>P90 (%)</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>Máx. (%)</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>A 0–2 %</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>B 2–4 %</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>C 4–8 %</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>D 8–15 %</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>E 15–25 %</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr">
+      <c r="S8" s="4" t="inlineStr">
         <is>
           <t>F 25–50 %</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr">
+      <c r="T8" s="4" t="inlineStr">
         <is>
           <t>G 50–75 %</t>
         </is>
       </c>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="U8" s="4" t="inlineStr">
         <is>
           <t>H &gt;75 %</t>
         </is>
       </c>
-      <c r="U8" s="4" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>Área &gt; 75 % (ha)</t>
         </is>
       </c>
-      <c r="V8" s="4" t="inlineStr">
+      <c r="W8" s="4" t="inlineStr">
         <is>
           <t>Ámbito de cálculo</t>
         </is>
@@ -726,54 +732,57 @@
         <v>78.154</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>613302</v>
+        <v>613335</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>9450231</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>58.39</v>
+        <v>9450201</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>78.154</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>56.84</v>
+        <v>60.18</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>85.7</v>
+        <v>60.63</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>137.32</v>
+        <v>86.16</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0</v>
+        <v>137.31</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="8" t="n">
         <v>0.23</v>
       </c>
-      <c r="P9" s="8" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Q9" s="8" t="n">
-        <v>4.09</v>
+        <v>1.15</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>33.1</v>
+        <v>6.34</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>40.94</v>
+        <v>24.8</v>
       </c>
       <c r="T9" s="8" t="n">
-        <v>20.58</v>
-      </c>
-      <c r="U9" s="9">
-        <f>F9*T9/100</f>
-        <v/>
-      </c>
-      <c r="V9" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>42.56</v>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v>24.91</v>
+      </c>
+      <c r="V9" s="9">
+        <f>F9*U9/100</f>
+        <v/>
+      </c>
+      <c r="W9" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -805,54 +814,57 @@
         <v>459.295</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>606816</v>
+        <v>606868</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>9458469</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>56.82</v>
+        <v>9458466</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>459.295</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>56.19</v>
+        <v>59.05</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>81.94</v>
+        <v>57.85</v>
       </c>
       <c r="L10" s="13" t="n">
+        <v>83.78</v>
+      </c>
+      <c r="M10" s="13" t="n">
         <v>179.01</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>0.02</v>
       </c>
       <c r="N10" s="13" t="n">
         <v>0.02</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>0.14</v>
+        <v>0.04</v>
       </c>
       <c r="P10" s="13" t="n">
-        <v>0.82</v>
+        <v>0.04</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>4.33</v>
+        <v>0.25</v>
       </c>
       <c r="R10" s="13" t="n">
-        <v>31.94</v>
+        <v>2.68</v>
       </c>
       <c r="S10" s="13" t="n">
-        <v>46.41</v>
+        <v>30.04</v>
       </c>
       <c r="T10" s="13" t="n">
-        <v>16.32</v>
-      </c>
-      <c r="U10" s="14">
-        <f>F10*T10/100</f>
-        <v/>
-      </c>
-      <c r="V10" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>49.47</v>
+      </c>
+      <c r="U10" s="13" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="V10" s="14">
+        <f>F10*U10/100</f>
+        <v/>
+      </c>
+      <c r="W10" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -884,25 +896,25 @@
         <v>24.843</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>606468</v>
+        <v>606427</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>9454689</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>78.48</v>
+        <v>9454632</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>24.843</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>73.48</v>
+        <v>62.09</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>108.37</v>
+        <v>63.04</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>126.5</v>
+        <v>79.08</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0</v>
+        <v>102.61</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>0</v>
@@ -917,21 +929,24 @@
         <v>0</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>48.75</v>
+        <v>22.42</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>46.59</v>
-      </c>
-      <c r="U11" s="9">
-        <f>F11*T11/100</f>
-        <v/>
-      </c>
-      <c r="V11" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>62.63</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="V11" s="9">
+        <f>F11*U11/100</f>
+        <v/>
+      </c>
+      <c r="W11" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -963,54 +978,57 @@
         <v>68.569</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>618523</v>
+        <v>618492</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>9448918</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>40.01</v>
+        <v>9448899</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>68.569</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>38.03</v>
+        <v>42.08</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>56.97</v>
+        <v>40.73</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>94.23</v>
+        <v>57.07</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>0</v>
+        <v>74.45</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="R12" s="13" t="n">
-        <v>76</v>
+        <v>1.72</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>18.53</v>
+        <v>76.03</v>
       </c>
       <c r="T12" s="13" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="U12" s="14">
-        <f>F12*T12/100</f>
-        <v/>
-      </c>
-      <c r="V12" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>22.25</v>
+      </c>
+      <c r="U12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="14">
+        <f>F12*U12/100</f>
+        <v/>
+      </c>
+      <c r="W12" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -1042,54 +1060,57 @@
         <v>77.666</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>631723</v>
+        <v>621634</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>9439702</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>62.07</v>
+        <v>9452921</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>77.666</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>55.81</v>
+        <v>52.13</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>111.1</v>
+        <v>52.22</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>158.19</v>
+        <v>66.84</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>37.29</v>
+        <v>0.93</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>37.88</v>
+        <v>39.77</v>
       </c>
       <c r="T13" s="8" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="U13" s="9">
-        <f>F13*T13/100</f>
-        <v/>
-      </c>
-      <c r="V13" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>56.74</v>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V13" s="9">
+        <f>F13*U13/100</f>
+        <v/>
+      </c>
+      <c r="W13" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -1121,54 +1142,57 @@
         <v>168.411</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>605636</v>
+        <v>605722</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>9455269</v>
-      </c>
-      <c r="I14" s="13" t="n">
-        <v>72.47</v>
+        <v>9455309</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>168.411</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>65.78</v>
+        <v>70.11</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>112.82</v>
+        <v>67.63</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>243.65</v>
+        <v>101.06</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>0</v>
+        <v>185.38</v>
       </c>
       <c r="N14" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="13" t="n">
         <v>0.11</v>
       </c>
-      <c r="P14" s="13" t="n">
-        <v>0.8</v>
-      </c>
       <c r="Q14" s="13" t="n">
-        <v>1.18</v>
+        <v>0.59</v>
       </c>
       <c r="R14" s="13" t="n">
-        <v>22.73</v>
+        <v>2.46</v>
       </c>
       <c r="S14" s="13" t="n">
-        <v>39.52</v>
+        <v>14.43</v>
       </c>
       <c r="T14" s="13" t="n">
-        <v>35.67</v>
-      </c>
-      <c r="U14" s="14">
-        <f>F14*T14/100</f>
-        <v/>
-      </c>
-      <c r="V14" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>47.35</v>
+      </c>
+      <c r="U14" s="13" t="n">
+        <v>35.06</v>
+      </c>
+      <c r="V14" s="14">
+        <f>F14*U14/100</f>
+        <v/>
+      </c>
+      <c r="W14" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -1200,54 +1224,57 @@
         <v>75.363</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>606173</v>
+        <v>606161</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>9447361</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>49</v>
+        <v>9447405</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>75.363</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>48.61</v>
+        <v>50.01</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>66.08</v>
+        <v>49.35</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>84.09999999999999</v>
+        <v>67.55</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0</v>
+        <v>87.81</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="8" t="n">
         <v>0.12</v>
       </c>
-      <c r="P15" s="8" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="Q15" s="8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="R15" s="8" t="n">
-        <v>53.06</v>
+        <v>1.08</v>
       </c>
       <c r="S15" s="8" t="n">
-        <v>41.42</v>
+        <v>51.56</v>
       </c>
       <c r="T15" s="8" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="U15" s="9">
-        <f>F15*T15/100</f>
-        <v/>
-      </c>
-      <c r="V15" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>43.3</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="V15" s="9">
+        <f>F15*U15/100</f>
+        <v/>
+      </c>
+      <c r="W15" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -1279,54 +1306,57 @@
         <v>74.02800000000001</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>608800</v>
+        <v>608834</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>9445585</v>
-      </c>
-      <c r="I16" s="13" t="n">
-        <v>54.09</v>
+        <v>9445570</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>74.02800000000001</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>56.74</v>
+        <v>55.72</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>72.20999999999999</v>
+        <v>58.23</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>84.45</v>
+        <v>74</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>0</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="N16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="P16" s="13" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>2.43</v>
+        <v>0.48</v>
       </c>
       <c r="R16" s="13" t="n">
-        <v>33.74</v>
+        <v>1.57</v>
       </c>
       <c r="S16" s="13" t="n">
-        <v>57.16</v>
+        <v>31.24</v>
       </c>
       <c r="T16" s="13" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="U16" s="14">
-        <f>F16*T16/100</f>
-        <v/>
-      </c>
-      <c r="V16" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>58.38</v>
+      </c>
+      <c r="U16" s="13" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="V16" s="14">
+        <f>F16*U16/100</f>
+        <v/>
+      </c>
+      <c r="W16" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -1358,54 +1388,57 @@
         <v>106.538</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>607036</v>
+        <v>607162</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>9446211</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>42.96</v>
+        <v>9446245</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>106.538</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>42.48</v>
+        <v>44.65</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>63.23</v>
+        <v>43.47</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>86.89</v>
+        <v>64.58</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.08</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>1.86</v>
+        <v>0.17</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>10.49</v>
+        <v>1.7</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>56.51</v>
+        <v>7.05</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>28</v>
+        <v>57.05</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U17" s="9">
-        <f>F17*T17/100</f>
-        <v/>
-      </c>
-      <c r="V17" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>31.07</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="V17" s="9">
+        <f>F17*U17/100</f>
+        <v/>
+      </c>
+      <c r="W17" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -1437,54 +1470,57 @@
         <v>258.837</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>608472</v>
+        <v>608580</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>9448056</v>
-      </c>
-      <c r="I18" s="13" t="n">
+        <v>9448092</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>258.837</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>59.16</v>
+      </c>
+      <c r="K18" s="13" t="n">
         <v>59.26</v>
       </c>
-      <c r="J18" s="13" t="n">
-        <v>58.36</v>
-      </c>
-      <c r="K18" s="13" t="n">
-        <v>87.95999999999999</v>
-      </c>
       <c r="L18" s="13" t="n">
-        <v>169.19</v>
+        <v>75.34</v>
       </c>
       <c r="M18" s="13" t="n">
+        <v>118.33</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="13" t="n">
         <v>0.03</v>
       </c>
-      <c r="N18" s="13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O18" s="13" t="n">
+      <c r="P18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="13" t="n">
         <v>0.24</v>
       </c>
-      <c r="P18" s="13" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Q18" s="13" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="R18" s="13" t="n">
-        <v>25.77</v>
-      </c>
       <c r="S18" s="13" t="n">
-        <v>46.5</v>
+        <v>22.98</v>
       </c>
       <c r="T18" s="13" t="n">
-        <v>20.35</v>
-      </c>
-      <c r="U18" s="14">
-        <f>F18*T18/100</f>
-        <v/>
-      </c>
-      <c r="V18" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>66.05</v>
+      </c>
+      <c r="U18" s="13" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="V18" s="14">
+        <f>F18*U18/100</f>
+        <v/>
+      </c>
+      <c r="W18" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -1516,26 +1552,26 @@
         <v>84.227</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>654604</v>
+        <v>654617</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>9417736</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>64.05</v>
+        <v>9417734</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>84.227</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>58.16</v>
+        <v>64.37</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>97.98999999999999</v>
+        <v>58.44</v>
       </c>
       <c r="L19" s="8" t="n">
+        <v>98.67</v>
+      </c>
+      <c r="M19" s="8" t="n">
         <v>154.59</v>
       </c>
-      <c r="M19" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="N19" s="8" t="n">
         <v>0</v>
       </c>
@@ -1546,24 +1582,27 @@
         <v>0</v>
       </c>
       <c r="Q19" s="8" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>29.84</v>
+        <v>0.32</v>
       </c>
       <c r="S19" s="8" t="n">
-        <v>43.85</v>
+        <v>29.81</v>
       </c>
       <c r="T19" s="8" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="U19" s="9">
-        <f>F19*T19/100</f>
-        <v/>
-      </c>
-      <c r="V19" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>42.74</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="V19" s="9">
+        <f>F19*U19/100</f>
+        <v/>
+      </c>
+      <c r="W19" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -1595,54 +1634,57 @@
         <v>90.15900000000001</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>652191</v>
+        <v>652192</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>9414358</v>
       </c>
-      <c r="I20" s="13" t="n">
-        <v>65.58</v>
+      <c r="I20" s="11" t="n">
+        <v>90.15900000000001</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>65.8</v>
+        <v>67.06</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>89.11</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="L20" s="13" t="n">
+        <v>90.97</v>
+      </c>
+      <c r="M20" s="13" t="n">
         <v>114.7</v>
       </c>
-      <c r="M20" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="13" t="n">
         <v>0.1</v>
       </c>
-      <c r="O20" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="P20" s="13" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="R20" s="13" t="n">
-        <v>17.12</v>
+        <v>0.7</v>
       </c>
       <c r="S20" s="13" t="n">
-        <v>53.75</v>
+        <v>15.58</v>
       </c>
       <c r="T20" s="13" t="n">
-        <v>28.23</v>
-      </c>
-      <c r="U20" s="14">
-        <f>F20*T20/100</f>
-        <v/>
-      </c>
-      <c r="V20" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>50.65</v>
+      </c>
+      <c r="U20" s="13" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="V20" s="14">
+        <f>F20*U20/100</f>
+        <v/>
+      </c>
+      <c r="W20" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -1674,25 +1716,25 @@
         <v>52.966</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>654188</v>
+        <v>654193</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>9422849</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>59.68</v>
+        <v>9422833</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>52.966</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>58.19</v>
+        <v>60.37</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>83.59999999999999</v>
+        <v>58.63</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>116.84</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0</v>
+        <v>115.63</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>0</v>
@@ -1704,24 +1746,27 @@
         <v>0</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>0.87</v>
+        <v>0.17</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>33.62</v>
+        <v>0.34</v>
       </c>
       <c r="S21" s="8" t="n">
-        <v>46.45</v>
+        <v>28.25</v>
       </c>
       <c r="T21" s="8" t="n">
-        <v>19.06</v>
-      </c>
-      <c r="U21" s="9">
-        <f>F21*T21/100</f>
-        <v/>
-      </c>
-      <c r="V21" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>54.97</v>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="V21" s="9">
+        <f>F21*U21/100</f>
+        <v/>
+      </c>
+      <c r="W21" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1798,25 @@
         <v>34.874</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>652758</v>
+        <v>652779</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>9424380</v>
-      </c>
-      <c r="I22" s="13" t="n">
-        <v>53.55</v>
+        <v>9424394</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>34.874</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>53.14</v>
+        <v>54.73</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>69.23</v>
+        <v>54.07</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>92.88</v>
+        <v>70.33</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>0</v>
+        <v>80.03</v>
       </c>
       <c r="N22" s="13" t="n">
         <v>0</v>
@@ -1783,24 +1828,27 @@
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R22" s="13" t="n">
-        <v>30.77</v>
+        <v>1.06</v>
       </c>
       <c r="S22" s="13" t="n">
-        <v>63.13</v>
+        <v>28.76</v>
       </c>
       <c r="T22" s="13" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="U22" s="14">
-        <f>F22*T22/100</f>
-        <v/>
-      </c>
-      <c r="V22" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>65.95999999999999</v>
+      </c>
+      <c r="U22" s="13" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="V22" s="14">
+        <f>F22*U22/100</f>
+        <v/>
+      </c>
+      <c r="W22" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -1832,25 +1880,25 @@
         <v>28.523</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>654137</v>
+        <v>654135</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>9424425</v>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>62.6</v>
+        <v>9424429</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>28.523</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>60.66</v>
+        <v>62.89</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>85.91</v>
+        <v>62.97</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>105.24</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0</v>
+        <v>97.08</v>
       </c>
       <c r="N23" s="8" t="n">
         <v>0</v>
@@ -1862,24 +1910,27 @@
         <v>0</v>
       </c>
       <c r="Q23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8" t="n">
         <v>0.32</v>
       </c>
-      <c r="R23" s="8" t="n">
-        <v>23.96</v>
-      </c>
       <c r="S23" s="8" t="n">
-        <v>53.67</v>
+        <v>19.17</v>
       </c>
       <c r="T23" s="8" t="n">
-        <v>22.04</v>
-      </c>
-      <c r="U23" s="9">
-        <f>F23*T23/100</f>
-        <v/>
-      </c>
-      <c r="V23" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>59.42</v>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="V23" s="9">
+        <f>F23*U23/100</f>
+        <v/>
+      </c>
+      <c r="W23" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -1911,25 +1962,25 @@
         <v>40.132</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>653850</v>
+        <v>653833</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>9426236</v>
-      </c>
-      <c r="I24" s="13" t="n">
-        <v>70.41</v>
+        <v>9426266</v>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>40.132</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>71.34</v>
+        <v>64.77</v>
       </c>
       <c r="K24" s="13" t="n">
-        <v>82.98999999999999</v>
+        <v>65.81</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>109.47</v>
+        <v>80.25</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>0</v>
+        <v>90.34</v>
       </c>
       <c r="N24" s="13" t="n">
         <v>0</v>
@@ -1944,21 +1995,24 @@
         <v>0</v>
       </c>
       <c r="R24" s="13" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="S24" s="13" t="n">
-        <v>61.21</v>
+        <v>12.33</v>
       </c>
       <c r="T24" s="13" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="U24" s="14">
-        <f>F24*T24/100</f>
-        <v/>
-      </c>
-      <c r="V24" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>66.14</v>
+      </c>
+      <c r="U24" s="13" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="V24" s="14">
+        <f>F24*U24/100</f>
+        <v/>
+      </c>
+      <c r="W24" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -1990,25 +2044,25 @@
         <v>50.459</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>655059</v>
+        <v>655052</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>9413845</v>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>74.18000000000001</v>
+        <v>9413847</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>50.459</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>73.72</v>
+        <v>73.12</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>91.92</v>
+        <v>73.83</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>148.05</v>
+        <v>89.02</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0</v>
+        <v>130.56</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>0</v>
@@ -2023,21 +2077,24 @@
         <v>0</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="S25" s="8" t="n">
-        <v>49.19</v>
+        <v>3.6</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>46.33</v>
-      </c>
-      <c r="U25" s="9">
-        <f>F25*T25/100</f>
-        <v/>
-      </c>
-      <c r="V25" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>49.73</v>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="V25" s="9">
+        <f>F25*U25/100</f>
+        <v/>
+      </c>
+      <c r="W25" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -2069,54 +2126,57 @@
         <v>102.335</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>652566</v>
+        <v>652562</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>9417311</v>
-      </c>
-      <c r="I26" s="13" t="n">
-        <v>61.95</v>
+        <v>9417338</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>102.335</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>60.19</v>
+        <v>66.37</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>90.76000000000001</v>
+        <v>65.14</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>142.35</v>
+        <v>100.03</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>0</v>
+        <v>164.78</v>
       </c>
       <c r="N26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="13" t="n">
         <v>0.09</v>
       </c>
-      <c r="O26" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="P26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="13" t="n">
         <v>0.18</v>
       </c>
-      <c r="Q26" s="13" t="n">
-        <v>1.24</v>
-      </c>
       <c r="R26" s="13" t="n">
-        <v>32.39</v>
+        <v>1.05</v>
       </c>
       <c r="S26" s="13" t="n">
-        <v>37.07</v>
+        <v>29.62</v>
       </c>
       <c r="T26" s="13" t="n">
-        <v>29.04</v>
-      </c>
-      <c r="U26" s="14">
-        <f>F26*T26/100</f>
-        <v/>
-      </c>
-      <c r="V26" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>33.13</v>
+      </c>
+      <c r="U26" s="13" t="n">
+        <v>35.93</v>
+      </c>
+      <c r="V26" s="14">
+        <f>F26*U26/100</f>
+        <v/>
+      </c>
+      <c r="W26" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -2148,54 +2208,57 @@
         <v>94.812</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>650305</v>
+        <v>650297</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>9402785</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>32.67</v>
+        <v>9402765</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>94.812</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>24.66</v>
+        <v>33.79</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>62.66</v>
+        <v>27.03</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>102.42</v>
+        <v>60.51</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>0</v>
+        <v>93.97</v>
       </c>
       <c r="N27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="8" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="P27" s="8" t="n">
-        <v>10.78</v>
+        <v>0.09</v>
       </c>
       <c r="Q27" s="8" t="n">
-        <v>39.69</v>
+        <v>5.22</v>
       </c>
       <c r="R27" s="8" t="n">
-        <v>29.58</v>
+        <v>40.04</v>
       </c>
       <c r="S27" s="8" t="n">
-        <v>13.74</v>
+        <v>36.15</v>
       </c>
       <c r="T27" s="8" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="U27" s="9">
-        <f>F27*T27/100</f>
-        <v/>
-      </c>
-      <c r="V27" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>14.52</v>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="V27" s="9">
+        <f>F27*U27/100</f>
+        <v/>
+      </c>
+      <c r="W27" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -2227,26 +2290,26 @@
         <v>8.929</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>641538</v>
+        <v>641517</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>9401360</v>
-      </c>
-      <c r="I28" s="13" t="n">
-        <v>30.24</v>
+        <v>9401350</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>8.929</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>28.51</v>
+        <v>29.43</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>44.1</v>
+        <v>27.98</v>
       </c>
       <c r="L28" s="13" t="n">
+        <v>43.41</v>
+      </c>
+      <c r="M28" s="13" t="n">
         <v>56.46</v>
       </c>
-      <c r="M28" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="N28" s="13" t="n">
         <v>0</v>
       </c>
@@ -2254,27 +2317,30 @@
         <v>0</v>
       </c>
       <c r="P28" s="13" t="n">
-        <v>6.38</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>27.66</v>
+        <v>9.09</v>
       </c>
       <c r="R28" s="13" t="n">
-        <v>61.7</v>
+        <v>28.28</v>
       </c>
       <c r="S28" s="13" t="n">
-        <v>4.26</v>
+        <v>57.58</v>
       </c>
       <c r="T28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" s="14">
-        <f>F28*T28/100</f>
-        <v/>
-      </c>
-      <c r="V28" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>5.05</v>
+      </c>
+      <c r="U28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="14">
+        <f>F28*U28/100</f>
+        <v/>
+      </c>
+      <c r="W28" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -2306,54 +2372,57 @@
         <v>35.774</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>657819</v>
+        <v>657794</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>9428541</v>
-      </c>
-      <c r="I29" s="8" t="n">
-        <v>57.04</v>
+        <v>9428554</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>35.774</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>58.44</v>
+        <v>56.17</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>76.13</v>
+        <v>56.77</v>
       </c>
       <c r="L29" s="8" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="M29" s="8" t="n">
         <v>94.59</v>
       </c>
-      <c r="M29" s="8" t="n">
-        <v>0.26</v>
-      </c>
       <c r="N29" s="8" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="P29" s="8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>2.55</v>
+        <v>1</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>26.53</v>
+        <v>2</v>
       </c>
       <c r="S29" s="8" t="n">
-        <v>57.65</v>
+        <v>29</v>
       </c>
       <c r="T29" s="8" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="U29" s="9">
-        <f>F29*T29/100</f>
-        <v/>
-      </c>
-      <c r="V29" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>57.5</v>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="V29" s="9">
+        <f>F29*U29/100</f>
+        <v/>
+      </c>
+      <c r="W29" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -2385,54 +2454,57 @@
         <v>90.90300000000001</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>655263</v>
+        <v>655341</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>9427340</v>
-      </c>
-      <c r="I30" s="13" t="n">
-        <v>43.16</v>
+        <v>9427395</v>
+      </c>
+      <c r="I30" s="11" t="n">
+        <v>90.90300000000001</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>42.43</v>
+        <v>40.22</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>63.94</v>
+        <v>38.36</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>109.11</v>
+        <v>60.42</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>0</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="N30" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="13" t="n">
         <v>0.79</v>
       </c>
-      <c r="P30" s="13" t="n">
-        <v>2.96</v>
-      </c>
       <c r="Q30" s="13" t="n">
-        <v>10.28</v>
+        <v>2.37</v>
       </c>
       <c r="R30" s="13" t="n">
-        <v>49.7</v>
+        <v>10.87</v>
       </c>
       <c r="S30" s="13" t="n">
-        <v>33</v>
+        <v>59.19</v>
       </c>
       <c r="T30" s="13" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="U30" s="14">
-        <f>F30*T30/100</f>
-        <v/>
-      </c>
-      <c r="V30" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>25.59</v>
+      </c>
+      <c r="U30" s="13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V30" s="14">
+        <f>F30*U30/100</f>
+        <v/>
+      </c>
+      <c r="W30" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -2464,25 +2536,25 @@
         <v>150.214</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>650830</v>
+        <v>650852</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>9382303</v>
-      </c>
-      <c r="I31" s="8" t="n">
-        <v>55.59</v>
+        <v>9382332</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>150.214</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>54.94</v>
+        <v>53.63</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>73.12</v>
+        <v>54.71</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>149.96</v>
+        <v>67.94</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>0</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>0</v>
@@ -2491,27 +2563,30 @@
         <v>0</v>
       </c>
       <c r="P31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="8" t="n">
         <v>0.36</v>
       </c>
-      <c r="Q31" s="8" t="n">
-        <v>2.71</v>
-      </c>
       <c r="R31" s="8" t="n">
-        <v>31.27</v>
+        <v>1.21</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>56.89</v>
+        <v>32.93</v>
       </c>
       <c r="T31" s="8" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="U31" s="9">
-        <f>F31*T31/100</f>
-        <v/>
-      </c>
-      <c r="V31" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>62.71</v>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V31" s="9">
+        <f>F31*U31/100</f>
+        <v/>
+      </c>
+      <c r="W31" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -2543,54 +2618,57 @@
         <v>83.327</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>652939</v>
+        <v>652955</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>9382105</v>
-      </c>
-      <c r="I32" s="13" t="n">
-        <v>41.34</v>
+        <v>9382118</v>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>83.327</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>40.7</v>
+        <v>42.36</v>
       </c>
       <c r="K32" s="13" t="n">
-        <v>60.27</v>
+        <v>40.02</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>79.64</v>
+        <v>65.91</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>0</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="N32" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="P32" s="13" t="n">
         <v>0.65</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>6.64</v>
+        <v>1.4</v>
       </c>
       <c r="R32" s="13" t="n">
-        <v>66.16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S32" s="13" t="n">
-        <v>25.35</v>
+        <v>54.37</v>
       </c>
       <c r="T32" s="13" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="U32" s="14">
-        <f>F32*T32/100</f>
-        <v/>
-      </c>
-      <c r="V32" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>33.23</v>
+      </c>
+      <c r="U32" s="13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V32" s="14">
+        <f>F32*U32/100</f>
+        <v/>
+      </c>
+      <c r="W32" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -2622,54 +2700,57 @@
         <v>103.617</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>656445</v>
+        <v>656458</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>9393180</v>
-      </c>
-      <c r="I33" s="8" t="n">
-        <v>53.07</v>
+        <v>9393128</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>103.617</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>55.23</v>
+        <v>56.33</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>67.27</v>
+        <v>57.56</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>81.67</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="N33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="8" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="P33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="8" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q33" s="8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R33" s="8" t="n">
-        <v>31.99</v>
-      </c>
       <c r="S33" s="8" t="n">
-        <v>62.66</v>
+        <v>22.06</v>
       </c>
       <c r="T33" s="8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U33" s="9">
-        <f>F33*T33/100</f>
-        <v/>
-      </c>
-      <c r="V33" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>76.2</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V33" s="9">
+        <f>F33*U33/100</f>
+        <v/>
+      </c>
+      <c r="W33" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -2701,26 +2782,26 @@
         <v>82.08799999999999</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>665942</v>
+        <v>665963</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>9391144</v>
-      </c>
-      <c r="I34" s="13" t="n">
-        <v>61.27</v>
+        <v>9391131</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>82.08799999999999</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>61.94</v>
+        <v>61.93</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>80.7</v>
+        <v>62.75</v>
       </c>
       <c r="L34" s="13" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="M34" s="13" t="n">
         <v>99.54000000000001</v>
       </c>
-      <c r="M34" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="N34" s="13" t="n">
         <v>0</v>
       </c>
@@ -2728,27 +2809,30 @@
         <v>0</v>
       </c>
       <c r="P34" s="13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.77</v>
+        <v>0.22</v>
       </c>
       <c r="R34" s="13" t="n">
-        <v>22.71</v>
+        <v>0.66</v>
       </c>
       <c r="S34" s="13" t="n">
-        <v>55.9</v>
+        <v>24.09</v>
       </c>
       <c r="T34" s="13" t="n">
-        <v>20.29</v>
-      </c>
-      <c r="U34" s="14">
-        <f>F34*T34/100</f>
-        <v/>
-      </c>
-      <c r="V34" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>50.5</v>
+      </c>
+      <c r="U34" s="13" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="V34" s="14">
+        <f>F34*U34/100</f>
+        <v/>
+      </c>
+      <c r="W34" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -2780,26 +2864,26 @@
         <v>81.334</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>649847</v>
+        <v>649840</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>9376260</v>
-      </c>
-      <c r="I35" s="8" t="n">
-        <v>47.77</v>
+        <v>9376268</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>81.334</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>47.7</v>
+        <v>47.11</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>58.84</v>
+        <v>46.89</v>
       </c>
       <c r="L35" s="8" t="n">
+        <v>58.82</v>
+      </c>
+      <c r="M35" s="8" t="n">
         <v>99.31999999999999</v>
       </c>
-      <c r="M35" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="N35" s="8" t="n">
         <v>0</v>
       </c>
@@ -2807,27 +2891,30 @@
         <v>0</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="R35" s="8" t="n">
-        <v>61.69</v>
+        <v>0.66</v>
       </c>
       <c r="S35" s="8" t="n">
-        <v>35.97</v>
+        <v>63.05</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U35" s="9">
-        <f>F35*T35/100</f>
-        <v/>
-      </c>
-      <c r="V35" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>34.62</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V35" s="9">
+        <f>F35*U35/100</f>
+        <v/>
+      </c>
+      <c r="W35" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -2859,25 +2946,25 @@
         <v>47.581</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>663334</v>
+        <v>663386</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>9392820</v>
-      </c>
-      <c r="I36" s="13" t="n">
-        <v>53.81</v>
+        <v>9392808</v>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>47.581</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>52.94</v>
+        <v>53.45</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>73.44</v>
+        <v>52.87</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>90.68000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>0</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N36" s="13" t="n">
         <v>0</v>
@@ -2886,27 +2973,30 @@
         <v>0</v>
       </c>
       <c r="P36" s="13" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>1.88</v>
+        <v>0.57</v>
       </c>
       <c r="R36" s="13" t="n">
-        <v>40.79</v>
+        <v>2.47</v>
       </c>
       <c r="S36" s="13" t="n">
-        <v>48.87</v>
+        <v>38.59</v>
       </c>
       <c r="T36" s="13" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="U36" s="14">
-        <f>F36*T36/100</f>
-        <v/>
-      </c>
-      <c r="V36" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>51.52</v>
+      </c>
+      <c r="U36" s="13" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="V36" s="14">
+        <f>F36*U36/100</f>
+        <v/>
+      </c>
+      <c r="W36" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -2938,54 +3028,57 @@
         <v>230.098</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>656549</v>
+        <v>656507</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>9382009</v>
-      </c>
-      <c r="I37" s="8" t="n">
-        <v>69.09999999999999</v>
+        <v>9381981</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>230.098</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>65.22</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>101.1</v>
+        <v>71.77</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>247.08</v>
+        <v>108.29</v>
       </c>
       <c r="M37" s="8" t="n">
-        <v>0</v>
+        <v>247.06</v>
       </c>
       <c r="N37" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="8" t="n">
         <v>0.04</v>
       </c>
-      <c r="P37" s="8" t="n">
-        <v>0.24</v>
-      </c>
       <c r="Q37" s="8" t="n">
-        <v>1.26</v>
+        <v>0.2</v>
       </c>
       <c r="R37" s="8" t="n">
-        <v>20.43</v>
+        <v>0.35</v>
       </c>
       <c r="S37" s="8" t="n">
-        <v>44.21</v>
+        <v>12.47</v>
       </c>
       <c r="T37" s="8" t="n">
-        <v>33.82</v>
-      </c>
-      <c r="U37" s="9">
-        <f>F37*T37/100</f>
-        <v/>
-      </c>
-      <c r="V37" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>42.18</v>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v>44.76</v>
+      </c>
+      <c r="V37" s="9">
+        <f>F37*U37/100</f>
+        <v/>
+      </c>
+      <c r="W37" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -3017,25 +3110,25 @@
         <v>64.923</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>660525</v>
+        <v>660514</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>9394327</v>
-      </c>
-      <c r="I38" s="13" t="n">
-        <v>53.53</v>
+        <v>9394314</v>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>64.923</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>49.26</v>
+        <v>49.15</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>76.56999999999999</v>
+        <v>48.21</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>108.8</v>
+        <v>60.82</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>0</v>
+        <v>90.05</v>
       </c>
       <c r="N38" s="13" t="n">
         <v>0</v>
@@ -3047,24 +3140,27 @@
         <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="R38" s="13" t="n">
-        <v>51.89</v>
+        <v>0.83</v>
       </c>
       <c r="S38" s="13" t="n">
-        <v>35.06</v>
+        <v>58.69</v>
       </c>
       <c r="T38" s="13" t="n">
-        <v>12.48</v>
-      </c>
-      <c r="U38" s="14">
-        <f>F38*T38/100</f>
-        <v/>
-      </c>
-      <c r="V38" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>38.25</v>
+      </c>
+      <c r="U38" s="13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V38" s="14">
+        <f>F38*U38/100</f>
+        <v/>
+      </c>
+      <c r="W38" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -3096,25 +3192,25 @@
         <v>22.927</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>656291</v>
+        <v>656296</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>9379096</v>
-      </c>
-      <c r="I39" s="8" t="n">
-        <v>61.28</v>
+        <v>9379076</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>22.927</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>62.93</v>
+        <v>62.39</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>78.37</v>
+        <v>63.08</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>99.41</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>0</v>
@@ -3123,27 +3219,30 @@
         <v>0</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="R39" s="8" t="n">
-        <v>17.2</v>
+        <v>0</v>
       </c>
       <c r="S39" s="8" t="n">
-        <v>63.6</v>
+        <v>20</v>
       </c>
       <c r="T39" s="8" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="U39" s="9">
-        <f>F39*T39/100</f>
-        <v/>
-      </c>
-      <c r="V39" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>61.6</v>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="V39" s="9">
+        <f>F39*U39/100</f>
+        <v/>
+      </c>
+      <c r="W39" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -3175,25 +3274,25 @@
         <v>13.065</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>666537</v>
+        <v>666511</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>9395918</v>
-      </c>
-      <c r="I40" s="13" t="n">
-        <v>45.22</v>
+        <v>9395924</v>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>13.065</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>46.11</v>
+        <v>51.79</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>70.13</v>
+        <v>52.17</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>83.34999999999999</v>
+        <v>71.06</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>0</v>
+        <v>89.61</v>
       </c>
       <c r="N40" s="13" t="n">
         <v>0</v>
@@ -3202,27 +3301,30 @@
         <v>0</v>
       </c>
       <c r="P40" s="13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>12.24</v>
+        <v>2.16</v>
       </c>
       <c r="R40" s="13" t="n">
-        <v>43.54</v>
+        <v>2.88</v>
       </c>
       <c r="S40" s="13" t="n">
-        <v>38.1</v>
+        <v>36.69</v>
       </c>
       <c r="T40" s="13" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="U40" s="14">
-        <f>F40*T40/100</f>
-        <v/>
-      </c>
-      <c r="V40" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>53.24</v>
+      </c>
+      <c r="U40" s="13" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="V40" s="14">
+        <f>F40*U40/100</f>
+        <v/>
+      </c>
+      <c r="W40" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -3254,25 +3356,25 @@
         <v>19.425</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>663291</v>
+        <v>663264</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>9392332</v>
-      </c>
-      <c r="I41" s="8" t="n">
-        <v>55.37</v>
+        <v>9392364</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>19.425</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>57.25</v>
+        <v>55.68</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>72.5</v>
+        <v>57.48</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>89.88</v>
+        <v>69.23</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>0</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>0</v>
@@ -3281,27 +3383,30 @@
         <v>0</v>
       </c>
       <c r="P41" s="8" t="n">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="Q41" s="8" t="n">
-        <v>0.93</v>
+        <v>0.48</v>
       </c>
       <c r="R41" s="8" t="n">
-        <v>32.87</v>
+        <v>0.96</v>
       </c>
       <c r="S41" s="8" t="n">
-        <v>57.41</v>
+        <v>26.79</v>
       </c>
       <c r="T41" s="8" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="U41" s="9">
-        <f>F41*T41/100</f>
-        <v/>
-      </c>
-      <c r="V41" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>70.33</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V41" s="9">
+        <f>F41*U41/100</f>
+        <v/>
+      </c>
+      <c r="W41" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -3333,25 +3438,25 @@
         <v>22.388</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>666781</v>
+        <v>666761</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>9395573</v>
-      </c>
-      <c r="I42" s="13" t="n">
-        <v>46.49</v>
+        <v>9395572</v>
+      </c>
+      <c r="I42" s="11" t="n">
+        <v>22.388</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>45.63</v>
+        <v>44.03</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>66.42</v>
+        <v>45.36</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>81.90000000000001</v>
+        <v>63.28</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>0</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="N42" s="13" t="n">
         <v>0</v>
@@ -3363,24 +3468,27 @@
         <v>0</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="R42" s="13" t="n">
-        <v>51.79</v>
+        <v>13.15</v>
       </c>
       <c r="S42" s="13" t="n">
-        <v>38.25</v>
+        <v>50.6</v>
       </c>
       <c r="T42" s="13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U42" s="14">
-        <f>F42*T42/100</f>
-        <v/>
-      </c>
-      <c r="V42" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>35.46</v>
+      </c>
+      <c r="U42" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V42" s="14">
+        <f>F42*U42/100</f>
+        <v/>
+      </c>
+      <c r="W42" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -3412,25 +3520,25 @@
         <v>10.673</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>652104</v>
+        <v>652065</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>9373045</v>
-      </c>
-      <c r="I43" s="8" t="n">
-        <v>45</v>
+        <v>9373072</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>10.673</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>45.37</v>
+        <v>55.17</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>59.72</v>
+        <v>56.47</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>69.2</v>
+        <v>69.13</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>0</v>
+        <v>74.73</v>
       </c>
       <c r="N43" s="8" t="n">
         <v>0</v>
@@ -3442,24 +3550,27 @@
         <v>0</v>
       </c>
       <c r="Q43" s="8" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="R43" s="8" t="n">
-        <v>55.26</v>
+        <v>0</v>
       </c>
       <c r="S43" s="8" t="n">
-        <v>40.35</v>
+        <v>31.36</v>
       </c>
       <c r="T43" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" s="9">
-        <f>F43*T43/100</f>
-        <v/>
-      </c>
-      <c r="V43" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>68.64</v>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="9">
+        <f>F43*U43/100</f>
+        <v/>
+      </c>
+      <c r="W43" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -3491,25 +3602,25 @@
         <v>12.398</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>662236</v>
+        <v>662248</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>9391211</v>
-      </c>
-      <c r="I44" s="13" t="n">
-        <v>52.87</v>
+        <v>9391220</v>
+      </c>
+      <c r="I44" s="11" t="n">
+        <v>12.398</v>
       </c>
       <c r="J44" s="13" t="n">
-        <v>52.58</v>
+        <v>54.2</v>
       </c>
       <c r="K44" s="13" t="n">
-        <v>67.97</v>
+        <v>53.26</v>
       </c>
       <c r="L44" s="13" t="n">
-        <v>73.7</v>
+        <v>69.94</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>0</v>
+        <v>80.92</v>
       </c>
       <c r="N44" s="13" t="n">
         <v>0</v>
@@ -3524,21 +3635,24 @@
         <v>0</v>
       </c>
       <c r="R44" s="13" t="n">
-        <v>40.71</v>
+        <v>0</v>
       </c>
       <c r="S44" s="13" t="n">
-        <v>59.29</v>
+        <v>36.76</v>
       </c>
       <c r="T44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="14">
-        <f>F44*T44/100</f>
-        <v/>
-      </c>
-      <c r="V44" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>61.03</v>
+      </c>
+      <c r="U44" s="13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="V44" s="14">
+        <f>F44*U44/100</f>
+        <v/>
+      </c>
+      <c r="W44" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -3570,25 +3684,25 @@
         <v>54.29</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>658547</v>
+        <v>658565</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>9395594</v>
-      </c>
-      <c r="I45" s="8" t="n">
-        <v>73.76000000000001</v>
+        <v>9395587</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>54.29</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>72.5</v>
+        <v>75.12</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>99.48</v>
+        <v>72.83</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>145.98</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>0</v>
+        <v>134.7</v>
       </c>
       <c r="N45" s="8" t="n">
         <v>0</v>
@@ -3597,27 +3711,30 @@
         <v>0</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="8" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="R45" s="8" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="S45" s="8" t="n">
-        <v>49.75</v>
+        <v>2.97</v>
       </c>
       <c r="T45" s="8" t="n">
-        <v>41.37</v>
-      </c>
-      <c r="U45" s="9">
-        <f>F45*T45/100</f>
-        <v/>
-      </c>
-      <c r="V45" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>54.79</v>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="V45" s="9">
+        <f>F45*U45/100</f>
+        <v/>
+      </c>
+      <c r="W45" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -3649,25 +3766,25 @@
         <v>19.615</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>657922</v>
+        <v>657936</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>9377477</v>
-      </c>
-      <c r="I46" s="13" t="n">
-        <v>45.14</v>
+        <v>9377456</v>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>19.615</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>47.49</v>
+        <v>50.79</v>
       </c>
       <c r="K46" s="13" t="n">
-        <v>64.20999999999999</v>
+        <v>50.64</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>93.72</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>0</v>
+        <v>84.52</v>
       </c>
       <c r="N46" s="13" t="n">
         <v>0</v>
@@ -3676,27 +3793,30 @@
         <v>0</v>
       </c>
       <c r="P46" s="13" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="13" t="n">
-        <v>12.73</v>
+        <v>0</v>
       </c>
       <c r="R46" s="13" t="n">
-        <v>47.27</v>
+        <v>4.72</v>
       </c>
       <c r="S46" s="13" t="n">
-        <v>36.82</v>
+        <v>41.51</v>
       </c>
       <c r="T46" s="13" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U46" s="14">
-        <f>F46*T46/100</f>
-        <v/>
-      </c>
-      <c r="V46" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>49.06</v>
+      </c>
+      <c r="U46" s="13" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="V46" s="14">
+        <f>F46*U46/100</f>
+        <v/>
+      </c>
+      <c r="W46" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -3728,54 +3848,57 @@
         <v>126.952</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>651673</v>
+        <v>651637</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>9373383</v>
-      </c>
-      <c r="I47" s="8" t="n">
-        <v>57</v>
+        <v>9373506</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>126.952</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>55.91</v>
+        <v>60.62</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>79.27</v>
+        <v>59.68</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>117.39</v>
+        <v>81.45</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>0</v>
+        <v>117.38</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O47" s="8" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="P47" s="8" t="n">
-        <v>0.57</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q47" s="8" t="n">
-        <v>2.65</v>
+        <v>0.14</v>
       </c>
       <c r="R47" s="8" t="n">
-        <v>31.69</v>
+        <v>1.43</v>
       </c>
       <c r="S47" s="8" t="n">
-        <v>50.21</v>
+        <v>23.88</v>
       </c>
       <c r="T47" s="8" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="U47" s="9">
-        <f>F47*T47/100</f>
-        <v/>
-      </c>
-      <c r="V47" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>57.16</v>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="V47" s="9">
+        <f>F47*U47/100</f>
+        <v/>
+      </c>
+      <c r="W47" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -3807,26 +3930,26 @@
         <v>28.83</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>657160</v>
+        <v>657156</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>9373050</v>
-      </c>
-      <c r="I48" s="13" t="n">
-        <v>65.63</v>
+        <v>9373038</v>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>28.83</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>68</v>
+        <v>65.87</v>
       </c>
       <c r="K48" s="13" t="n">
-        <v>82.56</v>
+        <v>66.78</v>
       </c>
       <c r="L48" s="13" t="n">
+        <v>82.45999999999999</v>
+      </c>
+      <c r="M48" s="13" t="n">
         <v>93.56</v>
       </c>
-      <c r="M48" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="N48" s="13" t="n">
         <v>0</v>
       </c>
@@ -3837,24 +3960,27 @@
         <v>0</v>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="R48" s="13" t="n">
-        <v>14.15</v>
+        <v>0</v>
       </c>
       <c r="S48" s="13" t="n">
-        <v>55.66</v>
+        <v>11.49</v>
       </c>
       <c r="T48" s="13" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="U48" s="14">
-        <f>F48*T48/100</f>
-        <v/>
-      </c>
-      <c r="V48" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>59.94</v>
+      </c>
+      <c r="U48" s="13" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="V48" s="14">
+        <f>F48*U48/100</f>
+        <v/>
+      </c>
+      <c r="W48" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -3886,54 +4012,57 @@
         <v>268.393</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>644546</v>
+        <v>644498</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>9389106</v>
-      </c>
-      <c r="I49" s="8" t="n">
-        <v>36.07</v>
+        <v>9389156</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>268.393</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>32.04</v>
+        <v>33.5</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>63.96</v>
+        <v>31.62</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>120.79</v>
+        <v>52.5</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>1.58</v>
+        <v>85.06</v>
       </c>
       <c r="N49" s="8" t="n">
-        <v>1.71</v>
+        <v>0.13</v>
       </c>
       <c r="O49" s="8" t="n">
-        <v>1.54</v>
+        <v>0.84</v>
       </c>
       <c r="P49" s="8" t="n">
-        <v>3.69</v>
+        <v>0.57</v>
       </c>
       <c r="Q49" s="8" t="n">
-        <v>19.1</v>
+        <v>2.89</v>
       </c>
       <c r="R49" s="8" t="n">
-        <v>51.01</v>
+        <v>19.94</v>
       </c>
       <c r="S49" s="8" t="n">
-        <v>17.33</v>
+        <v>63.58</v>
       </c>
       <c r="T49" s="8" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U49" s="9">
-        <f>F49*T49/100</f>
-        <v/>
-      </c>
-      <c r="V49" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>11.68</v>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="V49" s="9">
+        <f>F49*U49/100</f>
+        <v/>
+      </c>
+      <c r="W49" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -3965,54 +4094,57 @@
         <v>234.069</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>643474</v>
+        <v>643506</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>9385620</v>
-      </c>
-      <c r="I50" s="13" t="n">
-        <v>31.45</v>
+        <v>9385590</v>
+      </c>
+      <c r="I50" s="11" t="n">
+        <v>234.069</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>31.06</v>
+        <v>31.32</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>46.22</v>
+        <v>30.69</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>76.81</v>
+        <v>44.1</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>0.65</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="N50" s="13" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O50" s="13" t="n">
-        <v>1.92</v>
+        <v>0.08</v>
       </c>
       <c r="P50" s="13" t="n">
-        <v>3.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q50" s="13" t="n">
-        <v>16.97</v>
+        <v>4.02</v>
       </c>
       <c r="R50" s="13" t="n">
-        <v>68.47</v>
+        <v>19.71</v>
       </c>
       <c r="S50" s="13" t="n">
-        <v>6.95</v>
+        <v>71.05</v>
       </c>
       <c r="T50" s="13" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="U50" s="14">
-        <f>F50*T50/100</f>
-        <v/>
-      </c>
-      <c r="V50" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>4.33</v>
+      </c>
+      <c r="U50" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="14">
+        <f>F50*U50/100</f>
+        <v/>
+      </c>
+      <c r="W50" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -4044,54 +4176,57 @@
         <v>289.914</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>642775</v>
+        <v>642792</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>9388574</v>
-      </c>
-      <c r="I51" s="8" t="n">
-        <v>28.68</v>
+        <v>9388567</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>289.914</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>28.91</v>
+        <v>29.15</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>44.57</v>
+        <v>28.4</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>79.56999999999999</v>
+        <v>41.12</v>
       </c>
       <c r="M51" s="8" t="n">
-        <v>5.06</v>
+        <v>62.23</v>
       </c>
       <c r="N51" s="8" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O51" s="8" t="n">
-        <v>2.34</v>
+        <v>0.03</v>
       </c>
       <c r="P51" s="8" t="n">
-        <v>3.72</v>
+        <v>0.34</v>
       </c>
       <c r="Q51" s="8" t="n">
-        <v>23.11</v>
+        <v>3.23</v>
       </c>
       <c r="R51" s="8" t="n">
-        <v>58.03</v>
+        <v>30.46</v>
       </c>
       <c r="S51" s="8" t="n">
-        <v>4.9</v>
+        <v>64.23</v>
       </c>
       <c r="T51" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U51" s="9">
-        <f>F51*T51/100</f>
-        <v/>
-      </c>
-      <c r="V51" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>1.71</v>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="9">
+        <f>F51*U51/100</f>
+        <v/>
+      </c>
+      <c r="W51" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -4123,25 +4258,25 @@
         <v>46.962</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>649472</v>
+        <v>649480</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>9425705</v>
-      </c>
-      <c r="I52" s="13" t="n">
-        <v>65.91</v>
+        <v>9425729</v>
+      </c>
+      <c r="I52" s="11" t="n">
+        <v>46.962</v>
       </c>
       <c r="J52" s="13" t="n">
-        <v>65.33</v>
+        <v>66.05</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>90.7</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>124.72</v>
+        <v>90.59</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>0</v>
+        <v>123.84</v>
       </c>
       <c r="N52" s="13" t="n">
         <v>0</v>
@@ -4150,27 +4285,30 @@
         <v>0</v>
       </c>
       <c r="P52" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="13" t="n">
         <v>0.19</v>
       </c>
-      <c r="Q52" s="13" t="n">
-        <v>0.57</v>
-      </c>
       <c r="R52" s="13" t="n">
-        <v>18.06</v>
+        <v>0.19</v>
       </c>
       <c r="S52" s="13" t="n">
-        <v>53.04</v>
+        <v>17.82</v>
       </c>
       <c r="T52" s="13" t="n">
-        <v>28.14</v>
-      </c>
-      <c r="U52" s="14">
-        <f>F52*T52/100</f>
-        <v/>
-      </c>
-      <c r="V52" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>54.79</v>
+      </c>
+      <c r="U52" s="13" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="V52" s="14">
+        <f>F52*U52/100</f>
+        <v/>
+      </c>
+      <c r="W52" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -4202,25 +4340,25 @@
         <v>28.45</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>646483</v>
+        <v>646476</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>9426305</v>
-      </c>
-      <c r="I53" s="8" t="n">
-        <v>45.18</v>
+        <v>9426290</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>28.45</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>45.49</v>
+        <v>51.34</v>
       </c>
       <c r="K53" s="8" t="n">
-        <v>62.39</v>
+        <v>52.45</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>74.65000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="M53" s="8" t="n">
-        <v>0</v>
+        <v>78.34</v>
       </c>
       <c r="N53" s="8" t="n">
         <v>0</v>
@@ -4229,27 +4367,30 @@
         <v>0</v>
       </c>
       <c r="P53" s="8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="8" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="R53" s="8" t="n">
-        <v>53.9</v>
+        <v>3.17</v>
       </c>
       <c r="S53" s="8" t="n">
-        <v>38.96</v>
+        <v>38.41</v>
       </c>
       <c r="T53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" s="9">
-        <f>F53*T53/100</f>
-        <v/>
-      </c>
-      <c r="V53" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>57.78</v>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="V53" s="9">
+        <f>F53*U53/100</f>
+        <v/>
+      </c>
+      <c r="W53" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -4281,26 +4422,26 @@
         <v>35.491</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>649081</v>
+        <v>649084</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>9424506</v>
-      </c>
-      <c r="I54" s="13" t="n">
-        <v>44.57</v>
+        <v>9424511</v>
+      </c>
+      <c r="I54" s="11" t="n">
+        <v>35.491</v>
       </c>
       <c r="J54" s="13" t="n">
-        <v>45.4</v>
+        <v>44.19</v>
       </c>
       <c r="K54" s="13" t="n">
-        <v>57.85</v>
+        <v>44.89</v>
       </c>
       <c r="L54" s="13" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="M54" s="13" t="n">
         <v>65.77</v>
       </c>
-      <c r="M54" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="N54" s="13" t="n">
         <v>0</v>
       </c>
@@ -4311,24 +4452,27 @@
         <v>0</v>
       </c>
       <c r="Q54" s="13" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R54" s="13" t="n">
-        <v>68.78</v>
+        <v>3.35</v>
       </c>
       <c r="S54" s="13" t="n">
-        <v>28.04</v>
+        <v>68.3</v>
       </c>
       <c r="T54" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" s="14">
-        <f>F54*T54/100</f>
-        <v/>
-      </c>
-      <c r="V54" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>28.35</v>
+      </c>
+      <c r="U54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="14">
+        <f>F54*U54/100</f>
+        <v/>
+      </c>
+      <c r="W54" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -4360,25 +4504,25 @@
         <v>44.201</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>647123</v>
+        <v>647139</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>9427602</v>
       </c>
-      <c r="I55" s="8" t="n">
-        <v>45.55</v>
+      <c r="I55" s="6" t="n">
+        <v>44.201</v>
       </c>
       <c r="J55" s="8" t="n">
-        <v>44.38</v>
+        <v>44.97</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>62.92</v>
+        <v>44.26</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>86.52</v>
+        <v>60.45</v>
       </c>
       <c r="M55" s="8" t="n">
-        <v>0</v>
+        <v>78.17</v>
       </c>
       <c r="N55" s="8" t="n">
         <v>0</v>
@@ -4390,24 +4534,27 @@
         <v>0</v>
       </c>
       <c r="Q55" s="8" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R55" s="8" t="n">
-        <v>66.19</v>
+        <v>1.64</v>
       </c>
       <c r="S55" s="8" t="n">
-        <v>28.74</v>
+        <v>69.06</v>
       </c>
       <c r="T55" s="8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U55" s="9">
-        <f>F55*T55/100</f>
-        <v/>
-      </c>
-      <c r="V55" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>28.89</v>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="V55" s="9">
+        <f>F55*U55/100</f>
+        <v/>
+      </c>
+      <c r="W55" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -4439,26 +4586,26 @@
         <v>19.266</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>647350</v>
+        <v>647376</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>9427252</v>
-      </c>
-      <c r="I56" s="13" t="n">
-        <v>57.53</v>
+        <v>9427237</v>
+      </c>
+      <c r="I56" s="11" t="n">
+        <v>19.266</v>
       </c>
       <c r="J56" s="13" t="n">
-        <v>57.34</v>
+        <v>60.13</v>
       </c>
       <c r="K56" s="13" t="n">
-        <v>80.56999999999999</v>
+        <v>61.06</v>
       </c>
       <c r="L56" s="13" t="n">
+        <v>82.20999999999999</v>
+      </c>
+      <c r="M56" s="13" t="n">
         <v>99.29000000000001</v>
       </c>
-      <c r="M56" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="N56" s="13" t="n">
         <v>0</v>
       </c>
@@ -4469,24 +4616,27 @@
         <v>0</v>
       </c>
       <c r="Q56" s="13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="R56" s="13" t="n">
-        <v>34.27</v>
+        <v>0.95</v>
       </c>
       <c r="S56" s="13" t="n">
-        <v>44.13</v>
+        <v>28.44</v>
       </c>
       <c r="T56" s="13" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="U56" s="14">
-        <f>F56*T56/100</f>
-        <v/>
-      </c>
-      <c r="V56" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>49.29</v>
+      </c>
+      <c r="U56" s="13" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="V56" s="14">
+        <f>F56*U56/100</f>
+        <v/>
+      </c>
+      <c r="W56" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -4518,25 +4668,25 @@
         <v>26.826</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>646236</v>
+        <v>646235</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>9425052</v>
-      </c>
-      <c r="I57" s="8" t="n">
-        <v>41.97</v>
+        <v>9425055</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>26.826</v>
       </c>
       <c r="J57" s="8" t="n">
-        <v>43.09</v>
+        <v>42.09</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>54.79</v>
+        <v>43.05</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>69.81999999999999</v>
+        <v>53.66</v>
       </c>
       <c r="M57" s="8" t="n">
-        <v>0</v>
+        <v>69.81</v>
       </c>
       <c r="N57" s="8" t="n">
         <v>0</v>
@@ -4548,24 +4698,27 @@
         <v>0</v>
       </c>
       <c r="Q57" s="8" t="n">
-        <v>6.36</v>
+        <v>0.34</v>
       </c>
       <c r="R57" s="8" t="n">
-        <v>72.08</v>
+        <v>4.39</v>
       </c>
       <c r="S57" s="8" t="n">
-        <v>21.55</v>
+        <v>75.34</v>
       </c>
       <c r="T57" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" s="9">
-        <f>F57*T57/100</f>
-        <v/>
-      </c>
-      <c r="V57" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>19.93</v>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="9">
+        <f>F57*U57/100</f>
+        <v/>
+      </c>
+      <c r="W57" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -4597,25 +4750,25 @@
         <v>30.804</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>654607</v>
+        <v>654634</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9395038</v>
-      </c>
-      <c r="I58" s="13" t="n">
-        <v>63.51</v>
+        <v>9395006</v>
+      </c>
+      <c r="I58" s="11" t="n">
+        <v>30.804</v>
       </c>
       <c r="J58" s="13" t="n">
-        <v>62.62</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>84.52</v>
+        <v>69.05</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>101.54</v>
+        <v>85.19</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>0</v>
+        <v>101.53</v>
       </c>
       <c r="N58" s="13" t="n">
         <v>0</v>
@@ -4627,24 +4780,27 @@
         <v>0</v>
       </c>
       <c r="Q58" s="13" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="R58" s="13" t="n">
-        <v>16.07</v>
+        <v>1.79</v>
       </c>
       <c r="S58" s="13" t="n">
-        <v>59.52</v>
+        <v>5.97</v>
       </c>
       <c r="T58" s="13" t="n">
-        <v>23.51</v>
-      </c>
-      <c r="U58" s="14">
-        <f>F58*T58/100</f>
-        <v/>
-      </c>
-      <c r="V58" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>56.12</v>
+      </c>
+      <c r="U58" s="13" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="V58" s="14">
+        <f>F58*U58/100</f>
+        <v/>
+      </c>
+      <c r="W58" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -4676,54 +4832,57 @@
         <v>23.171</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>656489</v>
+        <v>656482</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>9395403</v>
       </c>
-      <c r="I59" s="8" t="n">
-        <v>62.29</v>
+      <c r="I59" s="6" t="n">
+        <v>23.171</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>63.62</v>
+        <v>64.05</v>
       </c>
       <c r="K59" s="8" t="n">
-        <v>79.69</v>
+        <v>64.58</v>
       </c>
       <c r="L59" s="8" t="n">
-        <v>100.6</v>
+        <v>81.42</v>
       </c>
       <c r="M59" s="8" t="n">
-        <v>0</v>
+        <v>100.61</v>
       </c>
       <c r="N59" s="8" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O59" s="8" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="P59" s="8" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="8" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="R59" s="8" t="n">
-        <v>15.6</v>
+        <v>0.39</v>
       </c>
       <c r="S59" s="8" t="n">
-        <v>62</v>
+        <v>10.42</v>
       </c>
       <c r="T59" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="U59" s="9">
-        <f>F59*T59/100</f>
-        <v/>
-      </c>
-      <c r="V59" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>66.8</v>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="V59" s="9">
+        <f>F59*U59/100</f>
+        <v/>
+      </c>
+      <c r="W59" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -4755,26 +4914,26 @@
         <v>28.234</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>663637</v>
+        <v>663654</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>9400618</v>
-      </c>
-      <c r="I60" s="13" t="n">
-        <v>41.78</v>
+        <v>9400590</v>
+      </c>
+      <c r="I60" s="11" t="n">
+        <v>28.234</v>
       </c>
       <c r="J60" s="13" t="n">
-        <v>42.36</v>
+        <v>41.35</v>
       </c>
       <c r="K60" s="13" t="n">
-        <v>55.97</v>
+        <v>42.2</v>
       </c>
       <c r="L60" s="13" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="M60" s="13" t="n">
         <v>69.54000000000001</v>
       </c>
-      <c r="M60" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="N60" s="13" t="n">
         <v>0</v>
       </c>
@@ -4782,27 +4941,30 @@
         <v>0</v>
       </c>
       <c r="P60" s="13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q60" s="13" t="n">
-        <v>7.59</v>
+        <v>1.61</v>
       </c>
       <c r="R60" s="13" t="n">
-        <v>69.3</v>
+        <v>9.35</v>
       </c>
       <c r="S60" s="13" t="n">
-        <v>21.52</v>
+        <v>63.55</v>
       </c>
       <c r="T60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="14">
-        <f>F60*T60/100</f>
-        <v/>
-      </c>
-      <c r="V60" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>25.48</v>
+      </c>
+      <c r="U60" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="14">
+        <f>F60*U60/100</f>
+        <v/>
+      </c>
+      <c r="W60" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -4834,25 +4996,25 @@
         <v>13.551</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>659649</v>
+        <v>659640</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>9401436</v>
-      </c>
-      <c r="I61" s="8" t="n">
-        <v>61.55</v>
+        <v>9401431</v>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>13.551</v>
       </c>
       <c r="J61" s="8" t="n">
-        <v>65.02</v>
+        <v>67.42</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>84.33</v>
+        <v>68.81</v>
       </c>
       <c r="L61" s="8" t="n">
-        <v>92.03</v>
+        <v>87.08</v>
       </c>
       <c r="M61" s="8" t="n">
-        <v>0</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="N61" s="8" t="n">
         <v>0</v>
@@ -4867,21 +5029,24 @@
         <v>0</v>
       </c>
       <c r="R61" s="8" t="n">
-        <v>33.11</v>
+        <v>0</v>
       </c>
       <c r="S61" s="8" t="n">
-        <v>39.19</v>
+        <v>18.92</v>
       </c>
       <c r="T61" s="8" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="U61" s="9">
-        <f>F61*T61/100</f>
-        <v/>
-      </c>
-      <c r="V61" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>45.27</v>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="V61" s="9">
+        <f>F61*U61/100</f>
+        <v/>
+      </c>
+      <c r="W61" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -4913,26 +5078,26 @@
         <v>13.184</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>654207</v>
+        <v>654210</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>9394210</v>
-      </c>
-      <c r="I62" s="13" t="n">
-        <v>59.32</v>
+        <v>9394211</v>
+      </c>
+      <c r="I62" s="11" t="n">
+        <v>13.184</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>61.1</v>
+        <v>58.84</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>71.38</v>
+        <v>60.65</v>
       </c>
       <c r="L62" s="13" t="n">
+        <v>71.31</v>
+      </c>
+      <c r="M62" s="13" t="n">
         <v>78.77</v>
       </c>
-      <c r="M62" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="N62" s="13" t="n">
         <v>0</v>
       </c>
@@ -4946,21 +5111,24 @@
         <v>0</v>
       </c>
       <c r="R62" s="13" t="n">
-        <v>21.77</v>
+        <v>0</v>
       </c>
       <c r="S62" s="13" t="n">
-        <v>74.15000000000001</v>
+        <v>22.6</v>
       </c>
       <c r="T62" s="13" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="U62" s="14">
-        <f>F62*T62/100</f>
-        <v/>
-      </c>
-      <c r="V62" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>73.97</v>
+      </c>
+      <c r="U62" s="13" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V62" s="14">
+        <f>F62*U62/100</f>
+        <v/>
+      </c>
+      <c r="W62" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -4992,54 +5160,57 @@
         <v>109.861</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>656578</v>
+        <v>656570</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>9397762</v>
-      </c>
-      <c r="I63" s="8" t="n">
-        <v>73.13</v>
+        <v>9397787</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>109.861</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>70.06999999999999</v>
+        <v>72.22</v>
       </c>
       <c r="K63" s="8" t="n">
-        <v>102.95</v>
+        <v>69.23</v>
       </c>
       <c r="L63" s="8" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="M63" s="8" t="n">
         <v>143.36</v>
       </c>
-      <c r="M63" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="N63" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O63" s="8" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="P63" s="8" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="Q63" s="8" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="R63" s="8" t="n">
-        <v>10.42</v>
+        <v>0.33</v>
       </c>
       <c r="S63" s="8" t="n">
-        <v>49.96</v>
+        <v>10.07</v>
       </c>
       <c r="T63" s="8" t="n">
-        <v>39.04</v>
-      </c>
-      <c r="U63" s="9">
-        <f>F63*T63/100</f>
-        <v/>
-      </c>
-      <c r="V63" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>52.74</v>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="V63" s="9">
+        <f>F63*U63/100</f>
+        <v/>
+      </c>
+      <c r="W63" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -5071,54 +5242,57 @@
         <v>279.68</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>641196</v>
+        <v>641305</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>9398710</v>
-      </c>
-      <c r="I64" s="13" t="n">
-        <v>37.42</v>
+        <v>9398784</v>
+      </c>
+      <c r="I64" s="11" t="n">
+        <v>279.68</v>
       </c>
       <c r="J64" s="13" t="n">
-        <v>39.19</v>
+        <v>28.42</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>63.42</v>
+        <v>26.26</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>98.37</v>
+        <v>50.43</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>0.9399999999999999</v>
+        <v>79.92</v>
       </c>
       <c r="N64" s="13" t="n">
-        <v>4.48</v>
+        <v>0.13</v>
       </c>
       <c r="O64" s="13" t="n">
-        <v>8</v>
+        <v>1.7</v>
       </c>
       <c r="P64" s="13" t="n">
-        <v>7.51</v>
+        <v>6.01</v>
       </c>
       <c r="Q64" s="13" t="n">
-        <v>8.77</v>
+        <v>15.31</v>
       </c>
       <c r="R64" s="13" t="n">
-        <v>40.12</v>
+        <v>24.05</v>
       </c>
       <c r="S64" s="13" t="n">
-        <v>26.83</v>
+        <v>42.25</v>
       </c>
       <c r="T64" s="13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U64" s="14">
-        <f>F64*T64/100</f>
-        <v/>
-      </c>
-      <c r="V64" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>10.42</v>
+      </c>
+      <c r="U64" s="13" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="V64" s="14">
+        <f>F64*U64/100</f>
+        <v/>
+      </c>
+      <c r="W64" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -5150,54 +5324,57 @@
         <v>55.17</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>664082</v>
+        <v>664088</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>9404172</v>
-      </c>
-      <c r="I65" s="8" t="n">
-        <v>33.94</v>
+        <v>9404177</v>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>55.17</v>
       </c>
       <c r="J65" s="8" t="n">
-        <v>34.77</v>
+        <v>35.85</v>
       </c>
       <c r="K65" s="8" t="n">
-        <v>47.26</v>
+        <v>36.63</v>
       </c>
       <c r="L65" s="8" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="M65" s="8" t="n">
         <v>56.5</v>
       </c>
-      <c r="M65" s="8" t="n">
-        <v>0.33</v>
-      </c>
       <c r="N65" s="8" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="O65" s="8" t="n">
-        <v>1.15</v>
+        <v>0.16</v>
       </c>
       <c r="P65" s="8" t="n">
-        <v>2.78</v>
+        <v>0.32</v>
       </c>
       <c r="Q65" s="8" t="n">
-        <v>14.89</v>
+        <v>1.94</v>
       </c>
       <c r="R65" s="8" t="n">
-        <v>77.09</v>
+        <v>13.41</v>
       </c>
       <c r="S65" s="8" t="n">
-        <v>3.27</v>
+        <v>80.94</v>
       </c>
       <c r="T65" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" s="9">
-        <f>F65*T65/100</f>
-        <v/>
-      </c>
-      <c r="V65" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>3.23</v>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="9">
+        <f>F65*U65/100</f>
+        <v/>
+      </c>
+      <c r="W65" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -5229,54 +5406,57 @@
         <v>116.099</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>639059</v>
+        <v>639029</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>9398295</v>
-      </c>
-      <c r="I66" s="13" t="n">
-        <v>37.21</v>
+        <v>9398251</v>
+      </c>
+      <c r="I66" s="11" t="n">
+        <v>116.099</v>
       </c>
       <c r="J66" s="13" t="n">
-        <v>38.77</v>
+        <v>36.62</v>
       </c>
       <c r="K66" s="13" t="n">
-        <v>64.40000000000001</v>
+        <v>38.12</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>81.84999999999999</v>
+        <v>65.63</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>0</v>
+        <v>83.2</v>
       </c>
       <c r="N66" s="13" t="n">
-        <v>0.77</v>
+        <v>0.15</v>
       </c>
       <c r="O66" s="13" t="n">
-        <v>10.53</v>
+        <v>0.85</v>
       </c>
       <c r="P66" s="13" t="n">
-        <v>12.15</v>
+        <v>12.16</v>
       </c>
       <c r="Q66" s="13" t="n">
-        <v>7.66</v>
+        <v>13.4</v>
       </c>
       <c r="R66" s="13" t="n">
-        <v>35.53</v>
+        <v>7.2</v>
       </c>
       <c r="S66" s="13" t="n">
-        <v>31.81</v>
+        <v>32.92</v>
       </c>
       <c r="T66" s="13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U66" s="14">
-        <f>F66*T66/100</f>
-        <v/>
-      </c>
-      <c r="V66" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>31.14</v>
+      </c>
+      <c r="U66" s="13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="V66" s="14">
+        <f>F66*U66/100</f>
+        <v/>
+      </c>
+      <c r="W66" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -5308,54 +5488,57 @@
         <v>295.726</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>617860</v>
+        <v>617863</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>9413182</v>
-      </c>
-      <c r="I67" s="8" t="n">
-        <v>26.8</v>
+        <v>9413165</v>
+      </c>
+      <c r="I67" s="6" t="n">
+        <v>295.726</v>
       </c>
       <c r="J67" s="8" t="n">
-        <v>29.53</v>
+        <v>34.55</v>
       </c>
       <c r="K67" s="8" t="n">
-        <v>50.04</v>
+        <v>36.08</v>
       </c>
       <c r="L67" s="8" t="n">
+        <v>51.56</v>
+      </c>
+      <c r="M67" s="8" t="n">
         <v>73.08</v>
       </c>
-      <c r="M67" s="8" t="n">
-        <v>8.220000000000001</v>
-      </c>
       <c r="N67" s="8" t="n">
-        <v>8.92</v>
+        <v>0.15</v>
       </c>
       <c r="O67" s="8" t="n">
-        <v>8.859999999999999</v>
+        <v>1.86</v>
       </c>
       <c r="P67" s="8" t="n">
-        <v>6.45</v>
+        <v>4.45</v>
       </c>
       <c r="Q67" s="8" t="n">
-        <v>10.89</v>
+        <v>5.79</v>
       </c>
       <c r="R67" s="8" t="n">
-        <v>46.62</v>
+        <v>11.11</v>
       </c>
       <c r="S67" s="8" t="n">
-        <v>10.04</v>
+        <v>63.55</v>
       </c>
       <c r="T67" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" s="9">
-        <f>F67*T67/100</f>
-        <v/>
-      </c>
-      <c r="V67" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>13.09</v>
+      </c>
+      <c r="U67" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="9">
+        <f>F67*U67/100</f>
+        <v/>
+      </c>
+      <c r="W67" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -5387,54 +5570,57 @@
         <v>160.36</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>621058</v>
+        <v>621088</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>9410427</v>
-      </c>
-      <c r="I68" s="13" t="n">
-        <v>34.23</v>
+        <v>9410445</v>
+      </c>
+      <c r="I68" s="11" t="n">
+        <v>160.36</v>
       </c>
       <c r="J68" s="13" t="n">
-        <v>35.75</v>
+        <v>37.8</v>
       </c>
       <c r="K68" s="13" t="n">
-        <v>53.08</v>
+        <v>37.87</v>
       </c>
       <c r="L68" s="13" t="n">
-        <v>70.83</v>
+        <v>53.36</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>1.51</v>
+        <v>68.36</v>
       </c>
       <c r="N68" s="13" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O68" s="13" t="n">
-        <v>5.05</v>
+        <v>0.34</v>
       </c>
       <c r="P68" s="13" t="n">
-        <v>4.32</v>
+        <v>0.45</v>
       </c>
       <c r="Q68" s="13" t="n">
-        <v>10.6</v>
+        <v>2.69</v>
       </c>
       <c r="R68" s="13" t="n">
-        <v>60.35</v>
+        <v>10.14</v>
       </c>
       <c r="S68" s="13" t="n">
-        <v>15.54</v>
+        <v>70.36</v>
       </c>
       <c r="T68" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" s="14">
-        <f>F68*T68/100</f>
-        <v/>
-      </c>
-      <c r="V68" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>16.02</v>
+      </c>
+      <c r="U68" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="14">
+        <f>F68*U68/100</f>
+        <v/>
+      </c>
+      <c r="W68" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -5466,54 +5652,57 @@
         <v>188.797</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>617695</v>
+        <v>617738</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>9409136</v>
-      </c>
-      <c r="I69" s="8" t="n">
-        <v>32.45</v>
+        <v>9409094</v>
+      </c>
+      <c r="I69" s="6" t="n">
+        <v>188.797</v>
       </c>
       <c r="J69" s="8" t="n">
         <v>34.29</v>
       </c>
       <c r="K69" s="8" t="n">
-        <v>48.5</v>
+        <v>34.75</v>
       </c>
       <c r="L69" s="8" t="n">
-        <v>67.53</v>
+        <v>47.36</v>
       </c>
       <c r="M69" s="8" t="n">
-        <v>0.57</v>
+        <v>80.41</v>
       </c>
       <c r="N69" s="8" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O69" s="8" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="P69" s="8" t="n">
-        <v>3.9</v>
+        <v>0.33</v>
       </c>
       <c r="Q69" s="8" t="n">
-        <v>16.45</v>
+        <v>2.05</v>
       </c>
       <c r="R69" s="8" t="n">
-        <v>63.58</v>
+        <v>19.74</v>
       </c>
       <c r="S69" s="8" t="n">
-        <v>7.61</v>
+        <v>72.44</v>
       </c>
       <c r="T69" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" s="9">
-        <f>F69*T69/100</f>
-        <v/>
-      </c>
-      <c r="V69" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>5.29</v>
+      </c>
+      <c r="U69" s="8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="V69" s="9">
+        <f>F69*U69/100</f>
+        <v/>
+      </c>
+      <c r="W69" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -5545,54 +5734,57 @@
         <v>249.89</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>618299</v>
+        <v>618239</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>9423119</v>
-      </c>
-      <c r="I70" s="13" t="n">
-        <v>35.29</v>
+        <v>9423110</v>
+      </c>
+      <c r="I70" s="11" t="n">
+        <v>249.89</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v>36.92</v>
+        <v>38.76</v>
       </c>
       <c r="K70" s="13" t="n">
-        <v>56.65</v>
+        <v>37.9</v>
       </c>
       <c r="L70" s="13" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="M70" s="13" t="n">
         <v>87.7</v>
       </c>
-      <c r="M70" s="13" t="n">
-        <v>1.09</v>
-      </c>
       <c r="N70" s="13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O70" s="13" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="P70" s="13" t="n">
-        <v>6.08</v>
+        <v>0.04</v>
       </c>
       <c r="Q70" s="13" t="n">
-        <v>12.6</v>
+        <v>3.14</v>
       </c>
       <c r="R70" s="13" t="n">
-        <v>51.74</v>
+        <v>13.3</v>
       </c>
       <c r="S70" s="13" t="n">
-        <v>19.26</v>
+        <v>64.06</v>
       </c>
       <c r="T70" s="13" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="U70" s="13" t="n">
         <v>0.83</v>
       </c>
-      <c r="U70" s="14">
-        <f>F70*T70/100</f>
-        <v/>
-      </c>
-      <c r="V70" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+      <c r="V70" s="14">
+        <f>F70*U70/100</f>
+        <v/>
+      </c>
+      <c r="W70" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -5624,54 +5816,57 @@
         <v>514.359</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>612864</v>
+        <v>612913</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>9413345</v>
-      </c>
-      <c r="I71" s="8" t="n">
-        <v>33.38</v>
+        <v>9413394</v>
+      </c>
+      <c r="I71" s="6" t="n">
+        <v>514.359</v>
       </c>
       <c r="J71" s="8" t="n">
-        <v>32.19</v>
+        <v>30.57</v>
       </c>
       <c r="K71" s="8" t="n">
-        <v>53.75</v>
+        <v>30.56</v>
       </c>
       <c r="L71" s="8" t="n">
-        <v>109.33</v>
+        <v>43.14</v>
       </c>
       <c r="M71" s="8" t="n">
-        <v>0.05</v>
+        <v>72.48</v>
       </c>
       <c r="N71" s="8" t="n">
-        <v>0.45</v>
+        <v>0.02</v>
       </c>
       <c r="O71" s="8" t="n">
-        <v>2.59</v>
+        <v>0.16</v>
       </c>
       <c r="P71" s="8" t="n">
-        <v>8.59</v>
+        <v>0.7</v>
       </c>
       <c r="Q71" s="8" t="n">
-        <v>19.37</v>
+        <v>5.21</v>
       </c>
       <c r="R71" s="8" t="n">
-        <v>55.41</v>
+        <v>23.97</v>
       </c>
       <c r="S71" s="8" t="n">
-        <v>12.02</v>
+        <v>66.45</v>
       </c>
       <c r="T71" s="8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U71" s="9">
-        <f>F71*T71/100</f>
-        <v/>
-      </c>
-      <c r="V71" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>3.5</v>
+      </c>
+      <c r="U71" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="9">
+        <f>F71*U71/100</f>
+        <v/>
+      </c>
+      <c r="W71" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -5703,54 +5898,57 @@
         <v>333.011</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>611196</v>
+        <v>611185</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>9416725</v>
-      </c>
-      <c r="I72" s="13" t="n">
-        <v>27.73</v>
+        <v>9416841</v>
+      </c>
+      <c r="I72" s="11" t="n">
+        <v>333.011</v>
       </c>
       <c r="J72" s="13" t="n">
-        <v>25.89</v>
+        <v>25.73</v>
       </c>
       <c r="K72" s="13" t="n">
-        <v>47.2</v>
+        <v>25.34</v>
       </c>
       <c r="L72" s="13" t="n">
-        <v>102.8</v>
+        <v>38.32</v>
       </c>
       <c r="M72" s="13" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="N72" s="13" t="n">
         <v>0.03</v>
       </c>
-      <c r="N72" s="13" t="n">
-        <v>0.24</v>
-      </c>
       <c r="O72" s="13" t="n">
-        <v>3.82</v>
+        <v>0.03</v>
       </c>
       <c r="P72" s="13" t="n">
-        <v>14.22</v>
+        <v>1.95</v>
       </c>
       <c r="Q72" s="13" t="n">
-        <v>29.24</v>
+        <v>11.46</v>
       </c>
       <c r="R72" s="13" t="n">
-        <v>45.52</v>
+        <v>35.08</v>
       </c>
       <c r="S72" s="13" t="n">
-        <v>6.53</v>
+        <v>50.38</v>
       </c>
       <c r="T72" s="13" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="U72" s="14">
-        <f>F72*T72/100</f>
-        <v/>
-      </c>
-      <c r="V72" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>1.08</v>
+      </c>
+      <c r="U72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="14">
+        <f>F72*U72/100</f>
+        <v/>
+      </c>
+      <c r="W72" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -5782,54 +5980,57 @@
         <v>160.978</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>611305</v>
+        <v>611325</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>9419274</v>
-      </c>
-      <c r="I73" s="8" t="n">
-        <v>36.37</v>
+        <v>9419328</v>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>160.978</v>
       </c>
       <c r="J73" s="8" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="K73" s="8" t="n">
         <v>36.48</v>
       </c>
-      <c r="K73" s="8" t="n">
-        <v>51.81</v>
-      </c>
       <c r="L73" s="8" t="n">
+        <v>52.36</v>
+      </c>
+      <c r="M73" s="8" t="n">
         <v>76.95999999999999</v>
       </c>
-      <c r="M73" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="N73" s="8" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="O73" s="8" t="n">
         <v>0.17</v>
       </c>
       <c r="P73" s="8" t="n">
-        <v>2.73</v>
+        <v>0.28</v>
       </c>
       <c r="Q73" s="8" t="n">
-        <v>16.73</v>
+        <v>3.07</v>
       </c>
       <c r="R73" s="8" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="S73" s="8" t="n">
         <v>67.31999999999999</v>
       </c>
-      <c r="S73" s="8" t="n">
-        <v>12.66</v>
-      </c>
       <c r="T73" s="8" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="U73" s="8" t="n">
         <v>0.28</v>
       </c>
-      <c r="U73" s="9">
-        <f>F73*T73/100</f>
-        <v/>
-      </c>
-      <c r="V73" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+      <c r="V73" s="9">
+        <f>F73*U73/100</f>
+        <v/>
+      </c>
+      <c r="W73" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -5861,25 +6062,25 @@
         <v>25.668</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>631195</v>
+        <v>631727</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>9441777</v>
-      </c>
-      <c r="I74" s="13" t="n">
-        <v>52.87</v>
+        <v>9439690</v>
+      </c>
+      <c r="I74" s="11" t="n">
+        <v>25.668</v>
       </c>
       <c r="J74" s="13" t="n">
-        <v>55.61</v>
+        <v>59.02</v>
       </c>
       <c r="K74" s="13" t="n">
-        <v>70.03</v>
+        <v>58.71</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>92.54000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>0</v>
+        <v>97.37</v>
       </c>
       <c r="N74" s="13" t="n">
         <v>0</v>
@@ -5888,27 +6089,30 @@
         <v>0</v>
       </c>
       <c r="P74" s="13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="13" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R74" s="13" t="n">
-        <v>31.45</v>
+        <v>0.7</v>
       </c>
       <c r="S74" s="13" t="n">
-        <v>56.89</v>
+        <v>28.42</v>
       </c>
       <c r="T74" s="13" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="U74" s="14">
-        <f>F74*T74/100</f>
-        <v/>
-      </c>
-      <c r="V74" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>56.84</v>
+      </c>
+      <c r="U74" s="13" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="V74" s="14">
+        <f>F74*U74/100</f>
+        <v/>
+      </c>
+      <c r="W74" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -5940,26 +6144,26 @@
         <v>13.554</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>631195</v>
+        <v>631204</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>9441777</v>
-      </c>
-      <c r="I75" s="8" t="n">
-        <v>58.13</v>
+        <v>9441778</v>
+      </c>
+      <c r="I75" s="6" t="n">
+        <v>13.554</v>
       </c>
       <c r="J75" s="8" t="n">
-        <v>61.35</v>
+        <v>60.92</v>
       </c>
       <c r="K75" s="8" t="n">
-        <v>75.33</v>
+        <v>62</v>
       </c>
       <c r="L75" s="8" t="n">
+        <v>75.42</v>
+      </c>
+      <c r="M75" s="8" t="n">
         <v>92.54000000000001</v>
       </c>
-      <c r="M75" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="N75" s="8" t="n">
         <v>0</v>
       </c>
@@ -5967,27 +6171,30 @@
         <v>0</v>
       </c>
       <c r="P75" s="8" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="8" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="R75" s="8" t="n">
-        <v>24.34</v>
+        <v>0</v>
       </c>
       <c r="S75" s="8" t="n">
-        <v>62.5</v>
+        <v>18.12</v>
       </c>
       <c r="T75" s="8" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="U75" s="9">
-        <f>F75*T75/100</f>
-        <v/>
-      </c>
-      <c r="V75" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>69.8</v>
+      </c>
+      <c r="U75" s="8" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="V75" s="9">
+        <f>F75*U75/100</f>
+        <v/>
+      </c>
+      <c r="W75" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -6019,54 +6226,57 @@
         <v>330.599</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>603653</v>
+        <v>603620</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>9439351</v>
-      </c>
-      <c r="I76" s="13" t="n">
-        <v>25.75</v>
+        <v>9439352</v>
+      </c>
+      <c r="I76" s="11" t="n">
+        <v>330.599</v>
       </c>
       <c r="J76" s="13" t="n">
-        <v>23.19</v>
+        <v>23.9</v>
       </c>
       <c r="K76" s="13" t="n">
-        <v>50.14</v>
+        <v>21.63</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>76.16</v>
+        <v>42.44</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>1.64</v>
+        <v>66.72</v>
       </c>
       <c r="N76" s="13" t="n">
-        <v>4.19</v>
+        <v>0.38</v>
       </c>
       <c r="O76" s="13" t="n">
-        <v>5.92</v>
+        <v>1.26</v>
       </c>
       <c r="P76" s="13" t="n">
-        <v>17.26</v>
+        <v>5.11</v>
       </c>
       <c r="Q76" s="13" t="n">
-        <v>25.5</v>
+        <v>20.02</v>
       </c>
       <c r="R76" s="13" t="n">
-        <v>35.28</v>
+        <v>33.48</v>
       </c>
       <c r="S76" s="13" t="n">
-        <v>10.19</v>
+        <v>35.5</v>
       </c>
       <c r="T76" s="13" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U76" s="14">
-        <f>F76*T76/100</f>
-        <v/>
-      </c>
-      <c r="V76" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>4.26</v>
+      </c>
+      <c r="U76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="14">
+        <f>F76*U76/100</f>
+        <v/>
+      </c>
+      <c r="W76" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -6098,54 +6308,57 @@
         <v>79.33</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>601122</v>
+        <v>601126</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>9443651</v>
-      </c>
-      <c r="I77" s="8" t="n">
-        <v>37.4</v>
+        <v>9443670</v>
+      </c>
+      <c r="I77" s="6" t="n">
+        <v>79.33</v>
       </c>
       <c r="J77" s="8" t="n">
-        <v>35.68</v>
+        <v>42.9</v>
       </c>
       <c r="K77" s="8" t="n">
-        <v>59.94</v>
+        <v>41.25</v>
       </c>
       <c r="L77" s="8" t="n">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="M77" s="8" t="n">
         <v>76.45</v>
       </c>
-      <c r="M77" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="N77" s="8" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="O77" s="8" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="P77" s="8" t="n">
-        <v>6.37</v>
+        <v>0.23</v>
       </c>
       <c r="Q77" s="8" t="n">
-        <v>14.11</v>
+        <v>5.58</v>
       </c>
       <c r="R77" s="8" t="n">
-        <v>56.54</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="S77" s="8" t="n">
-        <v>22.07</v>
+        <v>49.89</v>
       </c>
       <c r="T77" s="8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="U77" s="9">
-        <f>F77*T77/100</f>
-        <v/>
-      </c>
-      <c r="V77" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>34.62</v>
+      </c>
+      <c r="U77" s="8" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="V77" s="9">
+        <f>F77*U77/100</f>
+        <v/>
+      </c>
+      <c r="W77" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -6177,54 +6390,57 @@
         <v>68.887</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>596773</v>
+        <v>596769</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>9448273</v>
-      </c>
-      <c r="I78" s="13" t="n">
-        <v>25.05</v>
+        <v>9448285</v>
+      </c>
+      <c r="I78" s="11" t="n">
+        <v>68.887</v>
       </c>
       <c r="J78" s="13" t="n">
-        <v>23.25</v>
+        <v>24.8</v>
       </c>
       <c r="K78" s="13" t="n">
-        <v>46.38</v>
+        <v>23.28</v>
       </c>
       <c r="L78" s="13" t="n">
-        <v>67.53</v>
+        <v>39.91</v>
       </c>
       <c r="M78" s="13" t="n">
+        <v>53.67</v>
+      </c>
+      <c r="N78" s="13" t="n">
         <v>0.13</v>
       </c>
-      <c r="N78" s="13" t="n">
-        <v>1.59</v>
-      </c>
       <c r="O78" s="13" t="n">
-        <v>14.04</v>
+        <v>0.13</v>
       </c>
       <c r="P78" s="13" t="n">
-        <v>17.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q78" s="13" t="n">
-        <v>19.47</v>
+        <v>15.62</v>
       </c>
       <c r="R78" s="13" t="n">
-        <v>39.6</v>
+        <v>37.14</v>
       </c>
       <c r="S78" s="13" t="n">
-        <v>7.42</v>
+        <v>43.83</v>
       </c>
       <c r="T78" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" s="14">
-        <f>F78*T78/100</f>
-        <v/>
-      </c>
-      <c r="V78" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>1.05</v>
+      </c>
+      <c r="U78" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="14">
+        <f>F78*U78/100</f>
+        <v/>
+      </c>
+      <c r="W78" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -6256,54 +6472,57 @@
         <v>42.449</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>600644</v>
+        <v>600632</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>9440436</v>
-      </c>
-      <c r="I79" s="8" t="n">
-        <v>27.69</v>
+        <v>9440460</v>
+      </c>
+      <c r="I79" s="6" t="n">
+        <v>42.449</v>
       </c>
       <c r="J79" s="8" t="n">
-        <v>28.75</v>
+        <v>27</v>
       </c>
       <c r="K79" s="8" t="n">
-        <v>38.93</v>
+        <v>25.43</v>
       </c>
       <c r="L79" s="8" t="n">
+        <v>38.81</v>
+      </c>
+      <c r="M79" s="8" t="n">
         <v>47.36</v>
       </c>
-      <c r="M79" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="N79" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O79" s="8" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="P79" s="8" t="n">
-        <v>9.130000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="Q79" s="8" t="n">
-        <v>29.09</v>
+        <v>5.94</v>
       </c>
       <c r="R79" s="8" t="n">
-        <v>61.36</v>
+        <v>38.43</v>
       </c>
       <c r="S79" s="8" t="n">
-        <v>0</v>
+        <v>54.78</v>
       </c>
       <c r="T79" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="U79" s="9">
-        <f>F79*T79/100</f>
-        <v/>
-      </c>
-      <c r="V79" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+      <c r="U79" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="9">
+        <f>F79*U79/100</f>
+        <v/>
+      </c>
+      <c r="W79" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -6335,54 +6554,57 @@
         <v>124.709</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>604926</v>
+        <v>604678</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>9444327</v>
-      </c>
-      <c r="I80" s="13" t="n">
-        <v>37.25</v>
+        <v>9444376</v>
+      </c>
+      <c r="I80" s="11" t="n">
+        <v>124.709</v>
       </c>
       <c r="J80" s="13" t="n">
-        <v>33.29</v>
+        <v>35.04</v>
       </c>
       <c r="K80" s="13" t="n">
-        <v>66.64</v>
+        <v>34.6</v>
       </c>
       <c r="L80" s="13" t="n">
-        <v>96.58</v>
+        <v>51.22</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>0.14</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="N80" s="13" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="O80" s="13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P80" s="13" t="n">
-        <v>5.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q80" s="13" t="n">
-        <v>22.69</v>
+        <v>3.83</v>
       </c>
       <c r="R80" s="13" t="n">
-        <v>45.66</v>
+        <v>19.71</v>
       </c>
       <c r="S80" s="13" t="n">
-        <v>17.63</v>
+        <v>63.9</v>
       </c>
       <c r="T80" s="13" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="U80" s="14">
-        <f>F80*T80/100</f>
-        <v/>
-      </c>
-      <c r="V80" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>12.49</v>
+      </c>
+      <c r="U80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="14">
+        <f>F80*U80/100</f>
+        <v/>
+      </c>
+      <c r="W80" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -6414,54 +6636,57 @@
         <v>448.804</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>593246</v>
+        <v>593295</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>9430139</v>
-      </c>
-      <c r="I81" s="8" t="n">
-        <v>31.02</v>
+        <v>9430232</v>
+      </c>
+      <c r="I81" s="6" t="n">
+        <v>448.804</v>
       </c>
       <c r="J81" s="8" t="n">
-        <v>29.82</v>
+        <v>33.13</v>
       </c>
       <c r="K81" s="8" t="n">
-        <v>52.62</v>
+        <v>32.8</v>
       </c>
       <c r="L81" s="8" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="M81" s="8" t="n">
         <v>84.70999999999999</v>
       </c>
-      <c r="M81" s="8" t="n">
-        <v>1.1</v>
-      </c>
       <c r="N81" s="8" t="n">
-        <v>2.26</v>
+        <v>0.08</v>
       </c>
       <c r="O81" s="8" t="n">
-        <v>4.1</v>
+        <v>0.18</v>
       </c>
       <c r="P81" s="8" t="n">
-        <v>9.109999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="Q81" s="8" t="n">
-        <v>24.84</v>
+        <v>8.69</v>
       </c>
       <c r="R81" s="8" t="n">
-        <v>45.52</v>
+        <v>24.33</v>
       </c>
       <c r="S81" s="8" t="n">
-        <v>12.71</v>
+        <v>52.07</v>
       </c>
       <c r="T81" s="8" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="U81" s="8" t="n">
         <v>0.36</v>
       </c>
-      <c r="U81" s="9">
-        <f>F81*T81/100</f>
-        <v/>
-      </c>
-      <c r="V81" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+      <c r="V81" s="9">
+        <f>F81*U81/100</f>
+        <v/>
+      </c>
+      <c r="W81" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -6493,54 +6718,57 @@
         <v>355.364</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>595552</v>
+        <v>595641</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>9451222</v>
-      </c>
-      <c r="I82" s="13" t="n">
-        <v>16.64</v>
+        <v>9451287</v>
+      </c>
+      <c r="I82" s="11" t="n">
+        <v>355.364</v>
       </c>
       <c r="J82" s="13" t="n">
-        <v>13.3</v>
+        <v>18.27</v>
       </c>
       <c r="K82" s="13" t="n">
-        <v>36.71</v>
+        <v>15.41</v>
       </c>
       <c r="L82" s="13" t="n">
+        <v>37.39</v>
+      </c>
+      <c r="M82" s="13" t="n">
         <v>60.75</v>
       </c>
-      <c r="M82" s="13" t="n">
-        <v>4.77</v>
-      </c>
       <c r="N82" s="13" t="n">
-        <v>10.9</v>
+        <v>2.23</v>
       </c>
       <c r="O82" s="13" t="n">
-        <v>13.84</v>
+        <v>7.33</v>
       </c>
       <c r="P82" s="13" t="n">
-        <v>25.81</v>
+        <v>12.24</v>
       </c>
       <c r="Q82" s="13" t="n">
-        <v>21.12</v>
+        <v>26.59</v>
       </c>
       <c r="R82" s="13" t="n">
-        <v>22.74</v>
+        <v>25.17</v>
       </c>
       <c r="S82" s="13" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="T82" s="13" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="T82" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" s="14">
-        <f>F82*T82/100</f>
-        <v/>
-      </c>
-      <c r="V82" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+      <c r="U82" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="14">
+        <f>F82*U82/100</f>
+        <v/>
+      </c>
+      <c r="W82" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -6572,54 +6800,57 @@
         <v>74.372</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>617715</v>
+        <v>617686</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>9427284</v>
-      </c>
-      <c r="I83" s="8" t="n">
-        <v>40.47</v>
+        <v>9427289</v>
+      </c>
+      <c r="I83" s="6" t="n">
+        <v>74.372</v>
       </c>
       <c r="J83" s="8" t="n">
-        <v>40.27</v>
+        <v>40.25</v>
       </c>
       <c r="K83" s="8" t="n">
-        <v>65.73999999999999</v>
+        <v>39.94</v>
       </c>
       <c r="L83" s="8" t="n">
-        <v>89.98</v>
+        <v>62.33</v>
       </c>
       <c r="M83" s="8" t="n">
-        <v>0</v>
+        <v>80.89</v>
       </c>
       <c r="N83" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O83" s="8" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="P83" s="8" t="n">
-        <v>4.87</v>
+        <v>0.48</v>
       </c>
       <c r="Q83" s="8" t="n">
-        <v>22.29</v>
+        <v>2.42</v>
       </c>
       <c r="R83" s="8" t="n">
-        <v>38.73</v>
+        <v>18.67</v>
       </c>
       <c r="S83" s="8" t="n">
-        <v>31.3</v>
+        <v>49.33</v>
       </c>
       <c r="T83" s="8" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U83" s="9">
-        <f>F83*T83/100</f>
-        <v/>
-      </c>
-      <c r="V83" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>27.64</v>
+      </c>
+      <c r="U83" s="8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V83" s="9">
+        <f>F83*U83/100</f>
+        <v/>
+      </c>
+      <c r="W83" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -6651,25 +6882,25 @@
         <v>50.972</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>618248</v>
+        <v>618250</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>9426493</v>
-      </c>
-      <c r="I84" s="13" t="n">
-        <v>37.07</v>
+        <v>9426484</v>
+      </c>
+      <c r="I84" s="11" t="n">
+        <v>50.972</v>
       </c>
       <c r="J84" s="13" t="n">
-        <v>31.08</v>
+        <v>35.17</v>
       </c>
       <c r="K84" s="13" t="n">
-        <v>65.91</v>
+        <v>30.81</v>
       </c>
       <c r="L84" s="13" t="n">
-        <v>86.31</v>
+        <v>58.47</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>0</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="N84" s="13" t="n">
         <v>0</v>
@@ -6678,27 +6909,30 @@
         <v>0</v>
       </c>
       <c r="P84" s="13" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q84" s="13" t="n">
-        <v>29.2</v>
+        <v>2.28</v>
       </c>
       <c r="R84" s="13" t="n">
-        <v>40.71</v>
+        <v>27.42</v>
       </c>
       <c r="S84" s="13" t="n">
-        <v>21.42</v>
+        <v>50.62</v>
       </c>
       <c r="T84" s="13" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="U84" s="14">
-        <f>F84*T84/100</f>
-        <v/>
-      </c>
-      <c r="V84" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>19.68</v>
+      </c>
+      <c r="U84" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="14">
+        <f>F84*U84/100</f>
+        <v/>
+      </c>
+      <c r="W84" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -6730,54 +6964,57 @@
         <v>373.807</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>625311</v>
+        <v>625477</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>9412195</v>
-      </c>
-      <c r="I85" s="8" t="n">
-        <v>43.12</v>
+        <v>9412145</v>
+      </c>
+      <c r="I85" s="6" t="n">
+        <v>373.807</v>
       </c>
       <c r="J85" s="8" t="n">
-        <v>44.67</v>
+        <v>40.91</v>
       </c>
       <c r="K85" s="8" t="n">
-        <v>71.83</v>
+        <v>41.57</v>
       </c>
       <c r="L85" s="8" t="n">
-        <v>115.14</v>
+        <v>62.05</v>
       </c>
       <c r="M85" s="8" t="n">
-        <v>1.78</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="N85" s="8" t="n">
-        <v>2.24</v>
+        <v>0.05</v>
       </c>
       <c r="O85" s="8" t="n">
-        <v>3.49</v>
+        <v>0.36</v>
       </c>
       <c r="P85" s="8" t="n">
-        <v>6.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q85" s="8" t="n">
-        <v>10.7</v>
+        <v>4.43</v>
       </c>
       <c r="R85" s="8" t="n">
-        <v>33.96</v>
+        <v>12.35</v>
       </c>
       <c r="S85" s="8" t="n">
-        <v>33.45</v>
+        <v>50.77</v>
       </c>
       <c r="T85" s="8" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="U85" s="9">
-        <f>F85*T85/100</f>
-        <v/>
-      </c>
-      <c r="V85" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>28.67</v>
+      </c>
+      <c r="U85" s="8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V85" s="9">
+        <f>F85*U85/100</f>
+        <v/>
+      </c>
+      <c r="W85" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -6809,54 +7046,57 @@
         <v>81.795</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>635876</v>
+        <v>635900</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>9397941</v>
-      </c>
-      <c r="I86" s="13" t="n">
-        <v>27.94</v>
+        <v>9397976</v>
+      </c>
+      <c r="I86" s="11" t="n">
+        <v>81.795</v>
       </c>
       <c r="J86" s="13" t="n">
-        <v>29.58</v>
+        <v>31.94</v>
       </c>
       <c r="K86" s="13" t="n">
-        <v>41.7</v>
+        <v>33.04</v>
       </c>
       <c r="L86" s="13" t="n">
-        <v>56.99</v>
+        <v>44.92</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>2.11</v>
+        <v>61.93</v>
       </c>
       <c r="N86" s="13" t="n">
-        <v>3.11</v>
+        <v>2.08</v>
       </c>
       <c r="O86" s="13" t="n">
-        <v>2.55</v>
+        <v>0.66</v>
       </c>
       <c r="P86" s="13" t="n">
-        <v>6.66</v>
+        <v>0.88</v>
       </c>
       <c r="Q86" s="13" t="n">
-        <v>19.64</v>
+        <v>3.83</v>
       </c>
       <c r="R86" s="13" t="n">
-        <v>64.59</v>
+        <v>17.29</v>
       </c>
       <c r="S86" s="13" t="n">
-        <v>1.33</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="T86" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U86" s="14">
-        <f>F86*T86/100</f>
-        <v/>
-      </c>
-      <c r="V86" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>4.27</v>
+      </c>
+      <c r="U86" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="14">
+        <f>F86*U86/100</f>
+        <v/>
+      </c>
+      <c r="W86" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -6888,54 +7128,57 @@
         <v>30.909</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>639987</v>
+        <v>640013</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>9394392</v>
-      </c>
-      <c r="I87" s="8" t="n">
-        <v>15.99</v>
+        <v>9394399</v>
+      </c>
+      <c r="I87" s="6" t="n">
+        <v>30.909</v>
       </c>
       <c r="J87" s="8" t="n">
-        <v>14.46</v>
+        <v>14.36</v>
       </c>
       <c r="K87" s="8" t="n">
-        <v>23.27</v>
+        <v>13.57</v>
       </c>
       <c r="L87" s="8" t="n">
-        <v>56.79</v>
+        <v>20.47</v>
       </c>
       <c r="M87" s="8" t="n">
-        <v>0</v>
+        <v>34.78</v>
       </c>
       <c r="N87" s="8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O87" s="8" t="n">
-        <v>7.51</v>
+        <v>0.3</v>
       </c>
       <c r="P87" s="8" t="n">
-        <v>44.22</v>
+        <v>4.15</v>
       </c>
       <c r="Q87" s="8" t="n">
-        <v>38.44</v>
+        <v>55.79</v>
       </c>
       <c r="R87" s="8" t="n">
-        <v>7.8</v>
+        <v>37.69</v>
       </c>
       <c r="S87" s="8" t="n">
-        <v>0.58</v>
+        <v>2.08</v>
       </c>
       <c r="T87" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="U87" s="9">
-        <f>F87*T87/100</f>
-        <v/>
-      </c>
-      <c r="V87" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+      <c r="U87" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" s="9">
+        <f>F87*U87/100</f>
+        <v/>
+      </c>
+      <c r="W87" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -6967,54 +7210,57 @@
         <v>80.983</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>630685</v>
+        <v>630648</v>
       </c>
       <c r="H88" s="12" t="n">
         <v>9410800</v>
       </c>
-      <c r="I88" s="13" t="n">
-        <v>32.4</v>
+      <c r="I88" s="11" t="n">
+        <v>80.983</v>
       </c>
       <c r="J88" s="13" t="n">
-        <v>35.91</v>
+        <v>36.09</v>
       </c>
       <c r="K88" s="13" t="n">
-        <v>48.79</v>
+        <v>35.81</v>
       </c>
       <c r="L88" s="13" t="n">
-        <v>72.76000000000001</v>
+        <v>49.17</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>4.79</v>
+        <v>70.39</v>
       </c>
       <c r="N88" s="13" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O88" s="13" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="P88" s="13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q88" s="13" t="n">
-        <v>9.24</v>
+        <v>2</v>
       </c>
       <c r="R88" s="13" t="n">
-        <v>65.03</v>
+        <v>11.76</v>
       </c>
       <c r="S88" s="13" t="n">
-        <v>8.69</v>
+        <v>76.69</v>
       </c>
       <c r="T88" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" s="14">
-        <f>F88*T88/100</f>
-        <v/>
-      </c>
-      <c r="V88" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>9.539999999999999</v>
+      </c>
+      <c r="U88" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="14">
+        <f>F88*U88/100</f>
+        <v/>
+      </c>
+      <c r="W88" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -7046,54 +7292,57 @@
         <v>294.204</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>629338</v>
+        <v>629425</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>9413305</v>
-      </c>
-      <c r="I89" s="8" t="n">
-        <v>36.27</v>
+        <v>9413236</v>
+      </c>
+      <c r="I89" s="6" t="n">
+        <v>294.204</v>
       </c>
       <c r="J89" s="8" t="n">
-        <v>37.71</v>
+        <v>32.64</v>
       </c>
       <c r="K89" s="8" t="n">
-        <v>52.98</v>
+        <v>33.9</v>
       </c>
       <c r="L89" s="8" t="n">
-        <v>71.16</v>
+        <v>44.15</v>
       </c>
       <c r="M89" s="8" t="n">
-        <v>0.25</v>
+        <v>61.3</v>
       </c>
       <c r="N89" s="8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O89" s="8" t="n">
-        <v>1.72</v>
+        <v>0.06</v>
       </c>
       <c r="P89" s="8" t="n">
-        <v>4.5</v>
+        <v>1.86</v>
       </c>
       <c r="Q89" s="8" t="n">
-        <v>11.24</v>
+        <v>4.49</v>
       </c>
       <c r="R89" s="8" t="n">
-        <v>64.95999999999999</v>
+        <v>15.36</v>
       </c>
       <c r="S89" s="8" t="n">
-        <v>15.53</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="T89" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" s="9">
-        <f>F89*T89/100</f>
-        <v/>
-      </c>
-      <c r="V89" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>3.51</v>
+      </c>
+      <c r="U89" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="9">
+        <f>F89*U89/100</f>
+        <v/>
+      </c>
+      <c r="W89" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -7125,54 +7374,57 @@
         <v>130.425</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>629006</v>
+        <v>629089</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>9407536</v>
-      </c>
-      <c r="I90" s="13" t="n">
-        <v>25.24</v>
+        <v>9407681</v>
+      </c>
+      <c r="I90" s="11" t="n">
+        <v>130.425</v>
       </c>
       <c r="J90" s="13" t="n">
-        <v>30.07</v>
+        <v>31.78</v>
       </c>
       <c r="K90" s="13" t="n">
-        <v>43</v>
+        <v>33.85</v>
       </c>
       <c r="L90" s="13" t="n">
-        <v>57.22</v>
+        <v>45.27</v>
       </c>
       <c r="M90" s="13" t="n">
-        <v>8.84</v>
+        <v>57.08</v>
       </c>
       <c r="N90" s="13" t="n">
-        <v>10.84</v>
+        <v>1.59</v>
       </c>
       <c r="O90" s="13" t="n">
-        <v>5.73</v>
+        <v>4.97</v>
       </c>
       <c r="P90" s="13" t="n">
-        <v>4.63</v>
+        <v>1.79</v>
       </c>
       <c r="Q90" s="13" t="n">
-        <v>10.43</v>
+        <v>2.9</v>
       </c>
       <c r="R90" s="13" t="n">
-        <v>58.36</v>
+        <v>9.94</v>
       </c>
       <c r="S90" s="13" t="n">
-        <v>1.17</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="T90" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" s="14">
-        <f>F90*T90/100</f>
-        <v/>
-      </c>
-      <c r="V90" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>2.97</v>
+      </c>
+      <c r="U90" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="14">
+        <f>F90*U90/100</f>
+        <v/>
+      </c>
+      <c r="W90" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -7204,54 +7456,57 @@
         <v>115.379</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>631438</v>
+        <v>631484</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>9403547</v>
-      </c>
-      <c r="I91" s="8" t="n">
-        <v>23.48</v>
+        <v>9403551</v>
+      </c>
+      <c r="I91" s="6" t="n">
+        <v>115.379</v>
       </c>
       <c r="J91" s="8" t="n">
-        <v>24.71</v>
+        <v>24.64</v>
       </c>
       <c r="K91" s="8" t="n">
-        <v>43.53</v>
+        <v>25.06</v>
       </c>
       <c r="L91" s="8" t="n">
-        <v>62.74</v>
+        <v>39.93</v>
       </c>
       <c r="M91" s="8" t="n">
-        <v>3.08</v>
+        <v>56.49</v>
       </c>
       <c r="N91" s="8" t="n">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
       <c r="O91" s="8" t="n">
-        <v>15.3</v>
+        <v>2.76</v>
       </c>
       <c r="P91" s="8" t="n">
-        <v>6.15</v>
+        <v>10.24</v>
       </c>
       <c r="Q91" s="8" t="n">
-        <v>16.48</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="R91" s="8" t="n">
-        <v>45.9</v>
+        <v>27.48</v>
       </c>
       <c r="S91" s="8" t="n">
-        <v>3.71</v>
+        <v>48.9</v>
       </c>
       <c r="T91" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" s="9">
-        <f>F91*T91/100</f>
-        <v/>
-      </c>
-      <c r="V91" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>1.42</v>
+      </c>
+      <c r="U91" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="9">
+        <f>F91*U91/100</f>
+        <v/>
+      </c>
+      <c r="W91" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -7283,54 +7538,57 @@
         <v>65.745</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>633232</v>
+        <v>633308</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>9401227</v>
-      </c>
-      <c r="I92" s="13" t="n">
-        <v>31.7</v>
+        <v>9401252</v>
+      </c>
+      <c r="I92" s="11" t="n">
+        <v>65.745</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>31.95</v>
+        <v>36.41</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>46.4</v>
+        <v>36.32</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>76.73</v>
+        <v>51.87</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>0.28</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="N92" s="13" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>4.35</v>
+        <v>0.14</v>
       </c>
       <c r="P92" s="13" t="n">
-        <v>3.65</v>
+        <v>0.82</v>
       </c>
       <c r="Q92" s="13" t="n">
-        <v>15.99</v>
+        <v>3.68</v>
       </c>
       <c r="R92" s="13" t="n">
-        <v>66.48</v>
+        <v>13.51</v>
       </c>
       <c r="S92" s="13" t="n">
-        <v>6.59</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="T92" s="13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="U92" s="14">
-        <f>F92*T92/100</f>
-        <v/>
-      </c>
-      <c r="V92" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>13.1</v>
+      </c>
+      <c r="U92" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="14">
+        <f>F92*U92/100</f>
+        <v/>
+      </c>
+      <c r="W92" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -7362,54 +7620,57 @@
         <v>91.285</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>635110</v>
+        <v>635089</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>9399092</v>
-      </c>
-      <c r="I93" s="8" t="n">
-        <v>21.79</v>
+        <v>9399048</v>
+      </c>
+      <c r="I93" s="6" t="n">
+        <v>91.285</v>
       </c>
       <c r="J93" s="8" t="n">
-        <v>21.5</v>
+        <v>30.69</v>
       </c>
       <c r="K93" s="8" t="n">
-        <v>37.86</v>
+        <v>29.74</v>
       </c>
       <c r="L93" s="8" t="n">
-        <v>68.25</v>
+        <v>46.3</v>
       </c>
       <c r="M93" s="8" t="n">
-        <v>0.99</v>
+        <v>69.77</v>
       </c>
       <c r="N93" s="8" t="n">
-        <v>11.43</v>
+        <v>0</v>
       </c>
       <c r="O93" s="8" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="P93" s="8" t="n">
-        <v>13.1</v>
+        <v>0.1</v>
       </c>
       <c r="Q93" s="8" t="n">
-        <v>25.81</v>
+        <v>7.23</v>
       </c>
       <c r="R93" s="8" t="n">
-        <v>38.52</v>
+        <v>23.39</v>
       </c>
       <c r="S93" s="8" t="n">
-        <v>2.96</v>
+        <v>63.03</v>
       </c>
       <c r="T93" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" s="9">
-        <f>F93*T93/100</f>
-        <v/>
-      </c>
-      <c r="V93" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>6.24</v>
+      </c>
+      <c r="U93" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" s="9">
+        <f>F93*U93/100</f>
+        <v/>
+      </c>
+      <c r="W93" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -7441,54 +7702,57 @@
         <v>17.821</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>638648</v>
+        <v>638650</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>9411370</v>
-      </c>
-      <c r="I94" s="13" t="n">
-        <v>26.2</v>
+        <v>9411394</v>
+      </c>
+      <c r="I94" s="11" t="n">
+        <v>17.821</v>
       </c>
       <c r="J94" s="13" t="n">
-        <v>24.97</v>
+        <v>25.38</v>
       </c>
       <c r="K94" s="13" t="n">
-        <v>43.6</v>
+        <v>25.47</v>
       </c>
       <c r="L94" s="13" t="n">
-        <v>57.29</v>
+        <v>39.47</v>
       </c>
       <c r="M94" s="13" t="n">
-        <v>0</v>
+        <v>53.47</v>
       </c>
       <c r="N94" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O94" s="13" t="n">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="P94" s="13" t="n">
-        <v>13.78</v>
+        <v>3.08</v>
       </c>
       <c r="Q94" s="13" t="n">
-        <v>29.59</v>
+        <v>15.38</v>
       </c>
       <c r="R94" s="13" t="n">
-        <v>45.92</v>
+        <v>29.74</v>
       </c>
       <c r="S94" s="13" t="n">
-        <v>4.08</v>
+        <v>50.77</v>
       </c>
       <c r="T94" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" s="14">
-        <f>F94*T94/100</f>
-        <v/>
-      </c>
-      <c r="V94" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>1.03</v>
+      </c>
+      <c r="U94" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="14">
+        <f>F94*U94/100</f>
+        <v/>
+      </c>
+      <c r="W94" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -7520,54 +7784,57 @@
         <v>24.344</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>639720</v>
+        <v>639774</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>9410622</v>
-      </c>
-      <c r="I95" s="8" t="n">
-        <v>17.38</v>
+        <v>9410610</v>
+      </c>
+      <c r="I95" s="6" t="n">
+        <v>24.344</v>
       </c>
       <c r="J95" s="8" t="n">
-        <v>15.11</v>
+        <v>21.65</v>
       </c>
       <c r="K95" s="8" t="n">
-        <v>34.62</v>
+        <v>19.11</v>
       </c>
       <c r="L95" s="8" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="M95" s="8" t="n">
         <v>47.08</v>
       </c>
-      <c r="M95" s="8" t="n">
+      <c r="N95" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="8" t="n">
         <v>0.74</v>
       </c>
-      <c r="N95" s="8" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="O95" s="8" t="n">
-        <v>20.96</v>
-      </c>
       <c r="P95" s="8" t="n">
-        <v>23.53</v>
+        <v>9.59</v>
       </c>
       <c r="Q95" s="8" t="n">
-        <v>24.26</v>
+        <v>25.46</v>
       </c>
       <c r="R95" s="8" t="n">
-        <v>26.1</v>
+        <v>28.04</v>
       </c>
       <c r="S95" s="8" t="n">
-        <v>0</v>
+        <v>36.16</v>
       </c>
       <c r="T95" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="U95" s="9">
-        <f>F95*T95/100</f>
-        <v/>
-      </c>
-      <c r="V95" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+      <c r="U95" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="9">
+        <f>F95*U95/100</f>
+        <v/>
+      </c>
+      <c r="W95" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -7599,54 +7866,57 @@
         <v>5.097</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>640237</v>
+        <v>640243</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>9410714</v>
-      </c>
-      <c r="I96" s="13" t="n">
-        <v>21.01</v>
+        <v>9410706</v>
+      </c>
+      <c r="I96" s="11" t="n">
+        <v>5.097</v>
       </c>
       <c r="J96" s="13" t="n">
-        <v>20.46</v>
+        <v>21.18</v>
       </c>
       <c r="K96" s="13" t="n">
-        <v>34.65</v>
+        <v>21.57</v>
       </c>
       <c r="L96" s="13" t="n">
-        <v>49.72</v>
+        <v>29.46</v>
       </c>
       <c r="M96" s="13" t="n">
-        <v>0</v>
+        <v>33.8</v>
       </c>
       <c r="N96" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O96" s="13" t="n">
-        <v>12.96</v>
+        <v>0</v>
       </c>
       <c r="P96" s="13" t="n">
-        <v>18.52</v>
+        <v>1.89</v>
       </c>
       <c r="Q96" s="13" t="n">
-        <v>35.19</v>
+        <v>18.87</v>
       </c>
       <c r="R96" s="13" t="n">
-        <v>33.33</v>
+        <v>50.94</v>
       </c>
       <c r="S96" s="13" t="n">
-        <v>0</v>
+        <v>28.3</v>
       </c>
       <c r="T96" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="U96" s="14">
-        <f>F96*T96/100</f>
-        <v/>
-      </c>
-      <c r="V96" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+      <c r="U96" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="14">
+        <f>F96*U96/100</f>
+        <v/>
+      </c>
+      <c r="W96" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -7678,54 +7948,57 @@
         <v>11.906</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>642200</v>
+        <v>642226</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>9411072</v>
-      </c>
-      <c r="I97" s="8" t="n">
-        <v>22.62</v>
+        <v>9411077</v>
+      </c>
+      <c r="I97" s="6" t="n">
+        <v>11.906</v>
       </c>
       <c r="J97" s="8" t="n">
-        <v>22.32</v>
+        <v>26.46</v>
       </c>
       <c r="K97" s="8" t="n">
-        <v>37.16</v>
+        <v>27.12</v>
       </c>
       <c r="L97" s="8" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="M97" s="8" t="n">
         <v>49.16</v>
       </c>
-      <c r="M97" s="8" t="n">
-        <v>1.49</v>
-      </c>
       <c r="N97" s="8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O97" s="8" t="n">
-        <v>7.46</v>
+        <v>0</v>
       </c>
       <c r="P97" s="8" t="n">
-        <v>17.16</v>
+        <v>1.5</v>
       </c>
       <c r="Q97" s="8" t="n">
-        <v>28.36</v>
+        <v>10.53</v>
       </c>
       <c r="R97" s="8" t="n">
-        <v>43.28</v>
+        <v>32.33</v>
       </c>
       <c r="S97" s="8" t="n">
-        <v>0</v>
+        <v>55.64</v>
       </c>
       <c r="T97" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="U97" s="9">
-        <f>F97*T97/100</f>
-        <v/>
-      </c>
-      <c r="V97" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+      <c r="U97" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" s="9">
+        <f>F97*U97/100</f>
+        <v/>
+      </c>
+      <c r="W97" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -7757,54 +8030,57 @@
         <v>30.001</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>642415</v>
+        <v>642398</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>9410216</v>
-      </c>
-      <c r="I98" s="13" t="n">
-        <v>25.86</v>
+        <v>9410253</v>
+      </c>
+      <c r="I98" s="11" t="n">
+        <v>30.001</v>
       </c>
       <c r="J98" s="13" t="n">
-        <v>25.29</v>
+        <v>25.26</v>
       </c>
       <c r="K98" s="13" t="n">
-        <v>44.35</v>
+        <v>25.73</v>
       </c>
       <c r="L98" s="13" t="n">
+        <v>43.36</v>
+      </c>
+      <c r="M98" s="13" t="n">
         <v>62.07</v>
       </c>
-      <c r="M98" s="13" t="n">
+      <c r="N98" s="13" t="n">
         <v>0.3</v>
       </c>
-      <c r="N98" s="13" t="n">
-        <v>1.22</v>
-      </c>
       <c r="O98" s="13" t="n">
-        <v>5.18</v>
+        <v>5.12</v>
       </c>
       <c r="P98" s="13" t="n">
-        <v>16.46</v>
+        <v>6.33</v>
       </c>
       <c r="Q98" s="13" t="n">
-        <v>25.91</v>
+        <v>10.84</v>
       </c>
       <c r="R98" s="13" t="n">
-        <v>45.43</v>
+        <v>24.4</v>
       </c>
       <c r="S98" s="13" t="n">
-        <v>5.49</v>
+        <v>48.49</v>
       </c>
       <c r="T98" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" s="14">
-        <f>F98*T98/100</f>
-        <v/>
-      </c>
-      <c r="V98" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>4.52</v>
+      </c>
+      <c r="U98" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" s="14">
+        <f>F98*U98/100</f>
+        <v/>
+      </c>
+      <c r="W98" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -7836,54 +8112,57 @@
         <v>62.219</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>642882</v>
+        <v>642814</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>9411123</v>
-      </c>
-      <c r="I99" s="8" t="n">
-        <v>13.46</v>
+        <v>9411178</v>
+      </c>
+      <c r="I99" s="6" t="n">
+        <v>62.219</v>
       </c>
       <c r="J99" s="8" t="n">
-        <v>11.99</v>
+        <v>15.08</v>
       </c>
       <c r="K99" s="8" t="n">
-        <v>20.79</v>
+        <v>14.67</v>
       </c>
       <c r="L99" s="8" t="n">
-        <v>23.76</v>
+        <v>21.04</v>
       </c>
       <c r="M99" s="8" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="N99" s="8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="O99" s="8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="P99" s="8" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q99" s="8" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="R99" s="8" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="S99" s="8" t="n">
         <v>0.29</v>
       </c>
-      <c r="N99" s="8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="O99" s="8" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="P99" s="8" t="n">
-        <v>60.98</v>
-      </c>
-      <c r="Q99" s="8" t="n">
-        <v>33.24</v>
-      </c>
-      <c r="R99" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S99" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="T99" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="U99" s="9">
-        <f>F99*T99/100</f>
-        <v/>
-      </c>
-      <c r="V99" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+      <c r="U99" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" s="9">
+        <f>F99*U99/100</f>
+        <v/>
+      </c>
+      <c r="W99" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -7915,54 +8194,57 @@
         <v>106.027</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>642079</v>
+        <v>642102</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>9413823</v>
-      </c>
-      <c r="I100" s="13" t="n">
-        <v>37.77</v>
+        <v>9413756</v>
+      </c>
+      <c r="I100" s="11" t="n">
+        <v>106.027</v>
       </c>
       <c r="J100" s="13" t="n">
-        <v>37.69</v>
+        <v>33.35</v>
       </c>
       <c r="K100" s="13" t="n">
-        <v>55.64</v>
+        <v>32.74</v>
       </c>
       <c r="L100" s="13" t="n">
-        <v>69.34</v>
+        <v>48.87</v>
       </c>
       <c r="M100" s="13" t="n">
-        <v>0</v>
+        <v>67.14</v>
       </c>
       <c r="N100" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O100" s="13" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="P100" s="13" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="13" t="n">
-        <v>13.01</v>
+        <v>4.76</v>
       </c>
       <c r="R100" s="13" t="n">
-        <v>61.9</v>
+        <v>19.8</v>
       </c>
       <c r="S100" s="13" t="n">
-        <v>19.22</v>
+        <v>66.86</v>
       </c>
       <c r="T100" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" s="14">
-        <f>F100*T100/100</f>
-        <v/>
-      </c>
-      <c r="V100" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>8.58</v>
+      </c>
+      <c r="U100" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" s="14">
+        <f>F100*U100/100</f>
+        <v/>
+      </c>
+      <c r="W100" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -7994,54 +8276,57 @@
         <v>84.825</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>633015</v>
+        <v>632961</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>9411483</v>
-      </c>
-      <c r="I101" s="8" t="n">
-        <v>26.98</v>
+        <v>9411495</v>
+      </c>
+      <c r="I101" s="6" t="n">
+        <v>84.825</v>
       </c>
       <c r="J101" s="8" t="n">
-        <v>28.73</v>
+        <v>35.36</v>
       </c>
       <c r="K101" s="8" t="n">
-        <v>45.03</v>
+        <v>35.25</v>
       </c>
       <c r="L101" s="8" t="n">
-        <v>62.29</v>
+        <v>49.72</v>
       </c>
       <c r="M101" s="8" t="n">
-        <v>1.6</v>
+        <v>64.89</v>
       </c>
       <c r="N101" s="8" t="n">
-        <v>4.89</v>
+        <v>0.11</v>
       </c>
       <c r="O101" s="8" t="n">
-        <v>9.890000000000001</v>
+        <v>0</v>
       </c>
       <c r="P101" s="8" t="n">
-        <v>7.23</v>
+        <v>0</v>
       </c>
       <c r="Q101" s="8" t="n">
-        <v>16.91</v>
+        <v>2.55</v>
       </c>
       <c r="R101" s="8" t="n">
-        <v>56.06</v>
+        <v>16.68</v>
       </c>
       <c r="S101" s="8" t="n">
-        <v>3.4</v>
+        <v>71.09</v>
       </c>
       <c r="T101" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" s="9">
-        <f>F101*T101/100</f>
-        <v/>
-      </c>
-      <c r="V101" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>9.56</v>
+      </c>
+      <c r="U101" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="9">
+        <f>F101*U101/100</f>
+        <v/>
+      </c>
+      <c r="W101" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -8073,54 +8358,57 @@
         <v>52.743</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>635887</v>
+        <v>635828</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>9411738</v>
-      </c>
-      <c r="I102" s="13" t="n">
-        <v>31</v>
+        <v>9411731</v>
+      </c>
+      <c r="I102" s="11" t="n">
+        <v>52.743</v>
       </c>
       <c r="J102" s="13" t="n">
-        <v>31.66</v>
+        <v>35.08</v>
       </c>
       <c r="K102" s="13" t="n">
-        <v>48.48</v>
+        <v>34.58</v>
       </c>
       <c r="L102" s="13" t="n">
+        <v>48.98</v>
+      </c>
+      <c r="M102" s="13" t="n">
         <v>65.84</v>
       </c>
-      <c r="M102" s="13" t="n">
-        <v>0.53</v>
-      </c>
       <c r="N102" s="13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="O102" s="13" t="n">
-        <v>5.09</v>
+        <v>0.17</v>
       </c>
       <c r="P102" s="13" t="n">
-        <v>10</v>
+        <v>0.17</v>
       </c>
       <c r="Q102" s="13" t="n">
-        <v>17.19</v>
+        <v>3.22</v>
       </c>
       <c r="R102" s="13" t="n">
-        <v>58.25</v>
+        <v>15.93</v>
       </c>
       <c r="S102" s="13" t="n">
-        <v>7.89</v>
+        <v>71.53</v>
       </c>
       <c r="T102" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" s="14">
-        <f>F102*T102/100</f>
-        <v/>
-      </c>
-      <c r="V102" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>8.98</v>
+      </c>
+      <c r="U102" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="14">
+        <f>F102*U102/100</f>
+        <v/>
+      </c>
+      <c r="W102" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -8152,54 +8440,57 @@
         <v>60.352</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>637918</v>
+        <v>638003</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>9412134</v>
-      </c>
-      <c r="I103" s="8" t="n">
-        <v>42.1</v>
+        <v>9412154</v>
+      </c>
+      <c r="I103" s="6" t="n">
+        <v>60.352</v>
       </c>
       <c r="J103" s="8" t="n">
-        <v>44.16</v>
+        <v>45.26</v>
       </c>
       <c r="K103" s="8" t="n">
-        <v>57.14</v>
+        <v>45.73</v>
       </c>
       <c r="L103" s="8" t="n">
-        <v>73.18000000000001</v>
+        <v>68.11</v>
       </c>
       <c r="M103" s="8" t="n">
-        <v>0.15</v>
+        <v>83.22</v>
       </c>
       <c r="N103" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O103" s="8" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="P103" s="8" t="n">
-        <v>3.03</v>
+        <v>0.3</v>
       </c>
       <c r="Q103" s="8" t="n">
-        <v>8.77</v>
+        <v>1.94</v>
       </c>
       <c r="R103" s="8" t="n">
-        <v>60.21</v>
+        <v>8.52</v>
       </c>
       <c r="S103" s="8" t="n">
-        <v>27.69</v>
+        <v>51.87</v>
       </c>
       <c r="T103" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U103" s="9">
-        <f>F103*T103/100</f>
-        <v/>
-      </c>
-      <c r="V103" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>34.68</v>
+      </c>
+      <c r="U103" s="8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V103" s="9">
+        <f>F103*U103/100</f>
+        <v/>
+      </c>
+      <c r="W103" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -8231,54 +8522,57 @@
         <v>122.946</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>638309</v>
+        <v>638326</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>9415217</v>
-      </c>
-      <c r="I104" s="13" t="n">
-        <v>30.93</v>
+        <v>9415259</v>
+      </c>
+      <c r="I104" s="11" t="n">
+        <v>122.946</v>
       </c>
       <c r="J104" s="13" t="n">
-        <v>34.42</v>
+        <v>33.19</v>
       </c>
       <c r="K104" s="13" t="n">
-        <v>50.14</v>
+        <v>33.54</v>
       </c>
       <c r="L104" s="13" t="n">
-        <v>66.18000000000001</v>
+        <v>47.94</v>
       </c>
       <c r="M104" s="13" t="n">
-        <v>5.87</v>
+        <v>63.34</v>
       </c>
       <c r="N104" s="13" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O104" s="13" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="P104" s="13" t="n">
-        <v>6.75</v>
+        <v>0.52</v>
       </c>
       <c r="Q104" s="13" t="n">
-        <v>10.94</v>
+        <v>4.89</v>
       </c>
       <c r="R104" s="13" t="n">
-        <v>56.31</v>
+        <v>19.56</v>
       </c>
       <c r="S104" s="13" t="n">
-        <v>10.43</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="T104" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" s="14">
-        <f>F104*T104/100</f>
-        <v/>
-      </c>
-      <c r="V104" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>6.96</v>
+      </c>
+      <c r="U104" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" s="14">
+        <f>F104*U104/100</f>
+        <v/>
+      </c>
+      <c r="W104" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -8310,54 +8604,57 @@
         <v>565.5839999999999</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>632119</v>
+        <v>632116</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>9415141</v>
-      </c>
-      <c r="I105" s="8" t="n">
-        <v>17.74</v>
+        <v>9415177</v>
+      </c>
+      <c r="I105" s="6" t="n">
+        <v>565.5839999999999</v>
       </c>
       <c r="J105" s="8" t="n">
-        <v>13.46</v>
+        <v>24.65</v>
       </c>
       <c r="K105" s="8" t="n">
-        <v>39.23</v>
+        <v>26.46</v>
       </c>
       <c r="L105" s="8" t="n">
-        <v>62.83</v>
+        <v>42.47</v>
       </c>
       <c r="M105" s="8" t="n">
-        <v>8.460000000000001</v>
+        <v>65.75</v>
       </c>
       <c r="N105" s="8" t="n">
-        <v>17.4</v>
+        <v>1.69</v>
       </c>
       <c r="O105" s="8" t="n">
-        <v>15.84</v>
+        <v>6.7</v>
       </c>
       <c r="P105" s="8" t="n">
-        <v>10.5</v>
+        <v>11.98</v>
       </c>
       <c r="Q105" s="8" t="n">
-        <v>13.45</v>
+        <v>11.17</v>
       </c>
       <c r="R105" s="8" t="n">
-        <v>32.62</v>
+        <v>15.54</v>
       </c>
       <c r="S105" s="8" t="n">
-        <v>1.72</v>
+        <v>50.29</v>
       </c>
       <c r="T105" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" s="9">
-        <f>F105*T105/100</f>
-        <v/>
-      </c>
-      <c r="V105" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>2.63</v>
+      </c>
+      <c r="U105" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" s="9">
+        <f>F105*U105/100</f>
+        <v/>
+      </c>
+      <c r="W105" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -8389,28 +8686,28 @@
         <v>92.905</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>624397</v>
+        <v>624423</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>9437085</v>
-      </c>
-      <c r="I106" s="13" t="n">
-        <v>48.59</v>
+        <v>9437067</v>
+      </c>
+      <c r="I106" s="11" t="n">
+        <v>92.905</v>
       </c>
       <c r="J106" s="13" t="n">
-        <v>45.4</v>
+        <v>45.62</v>
       </c>
       <c r="K106" s="13" t="n">
-        <v>70.84999999999999</v>
+        <v>44.66</v>
       </c>
       <c r="L106" s="13" t="n">
+        <v>61.62</v>
+      </c>
+      <c r="M106" s="13" t="n">
         <v>134.31</v>
       </c>
-      <c r="M106" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="N106" s="13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O106" s="13" t="n">
         <v>0.1</v>
@@ -8419,24 +8716,27 @@
         <v>0.1</v>
       </c>
       <c r="Q106" s="13" t="n">
-        <v>1.95</v>
+        <v>0.19</v>
       </c>
       <c r="R106" s="13" t="n">
-        <v>58.97</v>
+        <v>2.33</v>
       </c>
       <c r="S106" s="13" t="n">
-        <v>30.51</v>
+        <v>62.98</v>
       </c>
       <c r="T106" s="13" t="n">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="U106" s="14">
-        <f>F106*T106/100</f>
-        <v/>
-      </c>
-      <c r="V106" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>31.4</v>
+      </c>
+      <c r="U106" s="13" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="V106" s="14">
+        <f>F106*U106/100</f>
+        <v/>
+      </c>
+      <c r="W106" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -8468,25 +8768,25 @@
         <v>80.616</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>625152</v>
+        <v>625114</v>
       </c>
       <c r="H107" s="7" t="n">
-        <v>9435011</v>
-      </c>
-      <c r="I107" s="8" t="n">
-        <v>54.02</v>
+        <v>9435040</v>
+      </c>
+      <c r="I107" s="6" t="n">
+        <v>80.616</v>
       </c>
       <c r="J107" s="8" t="n">
-        <v>54.39</v>
+        <v>55.98</v>
       </c>
       <c r="K107" s="8" t="n">
-        <v>77.27</v>
+        <v>55.05</v>
       </c>
       <c r="L107" s="8" t="n">
-        <v>93.02</v>
+        <v>79.59</v>
       </c>
       <c r="M107" s="8" t="n">
-        <v>0</v>
+        <v>102.6</v>
       </c>
       <c r="N107" s="8" t="n">
         <v>0</v>
@@ -8495,27 +8795,30 @@
         <v>0</v>
       </c>
       <c r="P107" s="8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Q107" s="8" t="n">
-        <v>3.6</v>
+        <v>0.89</v>
       </c>
       <c r="R107" s="8" t="n">
-        <v>35.25</v>
+        <v>2.68</v>
       </c>
       <c r="S107" s="8" t="n">
-        <v>47.52</v>
+        <v>34.34</v>
       </c>
       <c r="T107" s="8" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="U107" s="9">
-        <f>F107*T107/100</f>
-        <v/>
-      </c>
-      <c r="V107" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>45.97</v>
+      </c>
+      <c r="U107" s="8" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="V107" s="9">
+        <f>F107*U107/100</f>
+        <v/>
+      </c>
+      <c r="W107" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -8547,25 +8850,25 @@
         <v>11.475</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>619094</v>
+        <v>619097</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>9426406</v>
-      </c>
-      <c r="I108" s="13" t="n">
-        <v>30.46</v>
+        <v>9426385</v>
+      </c>
+      <c r="I108" s="11" t="n">
+        <v>11.475</v>
       </c>
       <c r="J108" s="13" t="n">
-        <v>28.32</v>
+        <v>28.45</v>
       </c>
       <c r="K108" s="13" t="n">
-        <v>42.6</v>
+        <v>27.53</v>
       </c>
       <c r="L108" s="13" t="n">
-        <v>49.96</v>
+        <v>36.16</v>
       </c>
       <c r="M108" s="13" t="n">
-        <v>0</v>
+        <v>48.06</v>
       </c>
       <c r="N108" s="13" t="n">
         <v>0</v>
@@ -8577,24 +8880,27 @@
         <v>0</v>
       </c>
       <c r="Q108" s="13" t="n">
-        <v>25.19</v>
+        <v>0</v>
       </c>
       <c r="R108" s="13" t="n">
-        <v>74.81</v>
+        <v>26.77</v>
       </c>
       <c r="S108" s="13" t="n">
-        <v>0</v>
+        <v>73.23</v>
       </c>
       <c r="T108" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="U108" s="14">
-        <f>F108*T108/100</f>
-        <v/>
-      </c>
-      <c r="V108" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+      <c r="U108" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="14">
+        <f>F108*U108/100</f>
+        <v/>
+      </c>
+      <c r="W108" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -8626,25 +8932,25 @@
         <v>28.19</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>626438</v>
+        <v>626489</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>9435060</v>
-      </c>
-      <c r="I109" s="8" t="n">
-        <v>61.03</v>
+        <v>9435047</v>
+      </c>
+      <c r="I109" s="6" t="n">
+        <v>28.19</v>
       </c>
       <c r="J109" s="8" t="n">
-        <v>62.35</v>
+        <v>60.16</v>
       </c>
       <c r="K109" s="8" t="n">
-        <v>78.7</v>
+        <v>59.93</v>
       </c>
       <c r="L109" s="8" t="n">
-        <v>100.61</v>
+        <v>78.14</v>
       </c>
       <c r="M109" s="8" t="n">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="N109" s="8" t="n">
         <v>0</v>
@@ -8653,27 +8959,30 @@
         <v>0</v>
       </c>
       <c r="P109" s="8" t="n">
-        <v>0.95</v>
+        <v>0.32</v>
       </c>
       <c r="Q109" s="8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="R109" s="8" t="n">
-        <v>19.94</v>
+        <v>1.61</v>
       </c>
       <c r="S109" s="8" t="n">
-        <v>55.38</v>
+        <v>20.26</v>
       </c>
       <c r="T109" s="8" t="n">
-        <v>22.15</v>
-      </c>
-      <c r="U109" s="9">
-        <f>F109*T109/100</f>
-        <v/>
-      </c>
-      <c r="V109" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>58.84</v>
+      </c>
+      <c r="U109" s="8" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="V109" s="9">
+        <f>F109*U109/100</f>
+        <v/>
+      </c>
+      <c r="W109" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -8705,26 +9014,26 @@
         <v>103.948</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>620759</v>
+        <v>620748</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>9439988</v>
-      </c>
-      <c r="I110" s="13" t="n">
-        <v>65.39</v>
+        <v>9439973</v>
+      </c>
+      <c r="I110" s="11" t="n">
+        <v>103.948</v>
       </c>
       <c r="J110" s="13" t="n">
-        <v>64.03</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="K110" s="13" t="n">
+        <v>63.87</v>
+      </c>
+      <c r="L110" s="13" t="n">
         <v>91.89</v>
       </c>
-      <c r="L110" s="13" t="n">
+      <c r="M110" s="13" t="n">
         <v>117.99</v>
       </c>
-      <c r="M110" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="N110" s="13" t="n">
         <v>0</v>
       </c>
@@ -8732,27 +9041,30 @@
         <v>0</v>
       </c>
       <c r="P110" s="13" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="Q110" s="13" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="R110" s="13" t="n">
-        <v>20.72</v>
+        <v>0</v>
       </c>
       <c r="S110" s="13" t="n">
-        <v>51.68</v>
+        <v>23.29</v>
       </c>
       <c r="T110" s="13" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="U110" s="14">
-        <f>F110*T110/100</f>
-        <v/>
-      </c>
-      <c r="V110" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>48.83</v>
+      </c>
+      <c r="U110" s="13" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="V110" s="14">
+        <f>F110*U110/100</f>
+        <v/>
+      </c>
+      <c r="W110" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -8784,26 +9096,26 @@
         <v>119.538</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>625419</v>
+        <v>625445</v>
       </c>
       <c r="H111" s="7" t="n">
         <v>9444932</v>
       </c>
-      <c r="I111" s="8" t="n">
-        <v>51.5</v>
+      <c r="I111" s="6" t="n">
+        <v>119.538</v>
       </c>
       <c r="J111" s="8" t="n">
-        <v>51.05</v>
+        <v>52.65</v>
       </c>
       <c r="K111" s="8" t="n">
-        <v>68.95999999999999</v>
+        <v>52.88</v>
       </c>
       <c r="L111" s="8" t="n">
+        <v>69.15000000000001</v>
+      </c>
+      <c r="M111" s="8" t="n">
         <v>97.04000000000001</v>
       </c>
-      <c r="M111" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="N111" s="8" t="n">
         <v>0</v>
       </c>
@@ -8814,24 +9126,27 @@
         <v>0</v>
       </c>
       <c r="Q111" s="8" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="R111" s="8" t="n">
-        <v>46.74</v>
+        <v>0.99</v>
       </c>
       <c r="S111" s="8" t="n">
-        <v>48.25</v>
+        <v>42.98</v>
       </c>
       <c r="T111" s="8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U111" s="9">
-        <f>F111*T111/100</f>
-        <v/>
-      </c>
-      <c r="V111" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>51.78</v>
+      </c>
+      <c r="U111" s="8" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="V111" s="9">
+        <f>F111*U111/100</f>
+        <v/>
+      </c>
+      <c r="W111" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -8863,54 +9178,57 @@
         <v>100.514</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>620263</v>
+        <v>620259</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>9442343</v>
-      </c>
-      <c r="I112" s="13" t="n">
-        <v>58.58</v>
+        <v>9442365</v>
+      </c>
+      <c r="I112" s="11" t="n">
+        <v>100.514</v>
       </c>
       <c r="J112" s="13" t="n">
-        <v>56.64</v>
+        <v>58.33</v>
       </c>
       <c r="K112" s="13" t="n">
-        <v>86.23999999999999</v>
+        <v>56.31</v>
       </c>
       <c r="L112" s="13" t="n">
+        <v>85.86</v>
+      </c>
+      <c r="M112" s="13" t="n">
         <v>147.72</v>
       </c>
-      <c r="M112" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="N112" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O112" s="13" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="P112" s="13" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="Q112" s="13" t="n">
-        <v>4.04</v>
+        <v>0.63</v>
       </c>
       <c r="R112" s="13" t="n">
-        <v>32.2</v>
+        <v>3.68</v>
       </c>
       <c r="S112" s="13" t="n">
-        <v>44.3</v>
+        <v>33.24</v>
       </c>
       <c r="T112" s="13" t="n">
-        <v>19.01</v>
-      </c>
-      <c r="U112" s="14">
-        <f>F112*T112/100</f>
-        <v/>
-      </c>
-      <c r="V112" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>43.49</v>
+      </c>
+      <c r="U112" s="13" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="V112" s="14">
+        <f>F112*U112/100</f>
+        <v/>
+      </c>
+      <c r="W112" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -8942,26 +9260,26 @@
         <v>86.14700000000001</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>620200</v>
+        <v>620253</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>9437862</v>
-      </c>
-      <c r="I113" s="8" t="n">
-        <v>49.21</v>
+        <v>9437857</v>
+      </c>
+      <c r="I113" s="6" t="n">
+        <v>86.14700000000001</v>
       </c>
       <c r="J113" s="8" t="n">
-        <v>45.08</v>
+        <v>51.23</v>
       </c>
       <c r="K113" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>45.5</v>
       </c>
       <c r="L113" s="8" t="n">
+        <v>79.22</v>
+      </c>
+      <c r="M113" s="8" t="n">
         <v>122.71</v>
       </c>
-      <c r="M113" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="N113" s="8" t="n">
         <v>0</v>
       </c>
@@ -8969,27 +9287,30 @@
         <v>0</v>
       </c>
       <c r="P113" s="8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q113" s="8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="R113" s="8" t="n">
-        <v>56.35</v>
+        <v>1.78</v>
       </c>
       <c r="S113" s="8" t="n">
-        <v>34.1</v>
+        <v>54.96</v>
       </c>
       <c r="T113" s="8" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="U113" s="9">
-        <f>F113*T113/100</f>
-        <v/>
-      </c>
-      <c r="V113" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>30.93</v>
+      </c>
+      <c r="U113" s="8" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="V113" s="9">
+        <f>F113*U113/100</f>
+        <v/>
+      </c>
+      <c r="W113" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -9021,25 +9342,25 @@
         <v>96.07899999999999</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>618661</v>
+        <v>618628</v>
       </c>
       <c r="H114" s="12" t="n">
-        <v>9438267</v>
-      </c>
-      <c r="I114" s="13" t="n">
-        <v>70.66</v>
+        <v>9438329</v>
+      </c>
+      <c r="I114" s="11" t="n">
+        <v>96.07899999999999</v>
       </c>
       <c r="J114" s="13" t="n">
-        <v>74.18000000000001</v>
+        <v>74.36</v>
       </c>
       <c r="K114" s="13" t="n">
-        <v>101</v>
+        <v>78.44</v>
       </c>
       <c r="L114" s="13" t="n">
-        <v>194.58</v>
+        <v>104.76</v>
       </c>
       <c r="M114" s="13" t="n">
-        <v>0</v>
+        <v>144.39</v>
       </c>
       <c r="N114" s="13" t="n">
         <v>0</v>
@@ -9048,27 +9369,30 @@
         <v>0</v>
       </c>
       <c r="P114" s="13" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Q114" s="13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="R114" s="13" t="n">
-        <v>24.5</v>
+        <v>0.37</v>
       </c>
       <c r="S114" s="13" t="n">
-        <v>25.07</v>
+        <v>20.62</v>
       </c>
       <c r="T114" s="13" t="n">
-        <v>48.91</v>
-      </c>
-      <c r="U114" s="14">
-        <f>F114*T114/100</f>
-        <v/>
-      </c>
-      <c r="V114" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>23.15</v>
+      </c>
+      <c r="U114" s="13" t="n">
+        <v>55.86</v>
+      </c>
+      <c r="V114" s="14">
+        <f>F114*U114/100</f>
+        <v/>
+      </c>
+      <c r="W114" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -9100,54 +9424,57 @@
         <v>81.776</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>619939</v>
+        <v>619979</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>9438544</v>
-      </c>
-      <c r="I115" s="8" t="n">
-        <v>63.63</v>
+        <v>9438580</v>
+      </c>
+      <c r="I115" s="6" t="n">
+        <v>81.776</v>
       </c>
       <c r="J115" s="8" t="n">
-        <v>65.55</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="K115" s="8" t="n">
-        <v>87.61</v>
+        <v>72.17</v>
       </c>
       <c r="L115" s="8" t="n">
+        <v>92.73999999999999</v>
+      </c>
+      <c r="M115" s="8" t="n">
         <v>123.35</v>
       </c>
-      <c r="M115" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="N115" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O115" s="8" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="P115" s="8" t="n">
         <v>0.11</v>
       </c>
       <c r="Q115" s="8" t="n">
-        <v>0.89</v>
+        <v>0.11</v>
       </c>
       <c r="R115" s="8" t="n">
-        <v>28.06</v>
+        <v>0.22</v>
       </c>
       <c r="S115" s="8" t="n">
-        <v>40.42</v>
+        <v>8.49</v>
       </c>
       <c r="T115" s="8" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="U115" s="9">
-        <f>F115*T115/100</f>
-        <v/>
-      </c>
-      <c r="V115" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>51.16</v>
+      </c>
+      <c r="U115" s="8" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="V115" s="9">
+        <f>F115*U115/100</f>
+        <v/>
+      </c>
+      <c r="W115" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -9179,26 +9506,26 @@
         <v>35.1</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>619630</v>
+        <v>619627</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>9440043</v>
-      </c>
-      <c r="I116" s="13" t="n">
-        <v>60.19</v>
+        <v>9440035</v>
+      </c>
+      <c r="I116" s="11" t="n">
+        <v>35.1</v>
       </c>
       <c r="J116" s="13" t="n">
-        <v>63.76</v>
+        <v>61.11</v>
       </c>
       <c r="K116" s="13" t="n">
-        <v>72.81</v>
+        <v>63.93</v>
       </c>
       <c r="L116" s="13" t="n">
+        <v>72.84</v>
+      </c>
+      <c r="M116" s="13" t="n">
         <v>83.70999999999999</v>
       </c>
-      <c r="M116" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="N116" s="13" t="n">
         <v>0</v>
       </c>
@@ -9209,24 +9536,27 @@
         <v>0</v>
       </c>
       <c r="Q116" s="13" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="R116" s="13" t="n">
-        <v>20.68</v>
+        <v>0.26</v>
       </c>
       <c r="S116" s="13" t="n">
-        <v>72.25</v>
+        <v>17.01</v>
       </c>
       <c r="T116" s="13" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="U116" s="14">
-        <f>F116*T116/100</f>
-        <v/>
-      </c>
-      <c r="V116" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>76.29000000000001</v>
+      </c>
+      <c r="U116" s="13" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="V116" s="14">
+        <f>F116*U116/100</f>
+        <v/>
+      </c>
+      <c r="W116" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -9258,26 +9588,26 @@
         <v>35.661</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>621452</v>
+        <v>621449</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>9443855</v>
-      </c>
-      <c r="I117" s="8" t="n">
-        <v>43.94</v>
+        <v>9443832</v>
+      </c>
+      <c r="I117" s="6" t="n">
+        <v>35.661</v>
       </c>
       <c r="J117" s="8" t="n">
-        <v>44.56</v>
+        <v>45.66</v>
       </c>
       <c r="K117" s="8" t="n">
-        <v>61.17</v>
+        <v>45.35</v>
       </c>
       <c r="L117" s="8" t="n">
+        <v>61.18</v>
+      </c>
+      <c r="M117" s="8" t="n">
         <v>75.20999999999999</v>
       </c>
-      <c r="M117" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="N117" s="8" t="n">
         <v>0</v>
       </c>
@@ -9285,27 +9615,30 @@
         <v>0</v>
       </c>
       <c r="P117" s="8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q117" s="8" t="n">
-        <v>8.470000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="R117" s="8" t="n">
-        <v>54.5</v>
+        <v>4.55</v>
       </c>
       <c r="S117" s="8" t="n">
-        <v>34.39</v>
+        <v>58.59</v>
       </c>
       <c r="T117" s="8" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="U117" s="9">
-        <f>F117*T117/100</f>
-        <v/>
-      </c>
-      <c r="V117" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>35.86</v>
+      </c>
+      <c r="U117" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V117" s="9">
+        <f>F117*U117/100</f>
+        <v/>
+      </c>
+      <c r="W117" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -9337,26 +9670,26 @@
         <v>34.171</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>620770</v>
+        <v>620814</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>9436562</v>
-      </c>
-      <c r="I118" s="13" t="n">
-        <v>56.47</v>
+        <v>9436572</v>
+      </c>
+      <c r="I118" s="11" t="n">
+        <v>34.171</v>
       </c>
       <c r="J118" s="13" t="n">
-        <v>55.21</v>
+        <v>55.22</v>
       </c>
       <c r="K118" s="13" t="n">
-        <v>73.42</v>
+        <v>54.16</v>
       </c>
       <c r="L118" s="13" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="M118" s="13" t="n">
         <v>88.79000000000001</v>
       </c>
-      <c r="M118" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="N118" s="13" t="n">
         <v>0</v>
       </c>
@@ -9364,27 +9697,30 @@
         <v>0</v>
       </c>
       <c r="P118" s="13" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="Q118" s="13" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="R118" s="13" t="n">
-        <v>33.95</v>
+        <v>0.8</v>
       </c>
       <c r="S118" s="13" t="n">
-        <v>58.42</v>
+        <v>34.49</v>
       </c>
       <c r="T118" s="13" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="U118" s="14">
-        <f>F118*T118/100</f>
-        <v/>
-      </c>
-      <c r="V118" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>57.75</v>
+      </c>
+      <c r="U118" s="13" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="V118" s="14">
+        <f>F118*U118/100</f>
+        <v/>
+      </c>
+      <c r="W118" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -9416,26 +9752,26 @@
         <v>35.347</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>617596</v>
+        <v>617584</v>
       </c>
       <c r="H119" s="7" t="n">
-        <v>9436227</v>
-      </c>
-      <c r="I119" s="8" t="n">
-        <v>47.98</v>
+        <v>9436232</v>
+      </c>
+      <c r="I119" s="6" t="n">
+        <v>35.347</v>
       </c>
       <c r="J119" s="8" t="n">
-        <v>48.84</v>
+        <v>47.04</v>
       </c>
       <c r="K119" s="8" t="n">
-        <v>59.94</v>
+        <v>46.9</v>
       </c>
       <c r="L119" s="8" t="n">
+        <v>60.04</v>
+      </c>
+      <c r="M119" s="8" t="n">
         <v>69.95</v>
       </c>
-      <c r="M119" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="N119" s="8" t="n">
         <v>0</v>
       </c>
@@ -9446,24 +9782,27 @@
         <v>0</v>
       </c>
       <c r="Q119" s="8" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R119" s="8" t="n">
-        <v>49.11</v>
+        <v>3.61</v>
       </c>
       <c r="S119" s="8" t="n">
-        <v>46.82</v>
+        <v>55.41</v>
       </c>
       <c r="T119" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U119" s="9">
-        <f>F119*T119/100</f>
-        <v/>
-      </c>
-      <c r="V119" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>40.98</v>
+      </c>
+      <c r="U119" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" s="9">
+        <f>F119*U119/100</f>
+        <v/>
+      </c>
+      <c r="W119" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -9495,25 +9834,25 @@
         <v>15.839</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>642334</v>
+        <v>642333</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>9438263</v>
-      </c>
-      <c r="I120" s="13" t="n">
-        <v>49.86</v>
+        <v>9438265</v>
+      </c>
+      <c r="I120" s="11" t="n">
+        <v>15.839</v>
       </c>
       <c r="J120" s="13" t="n">
-        <v>50.61</v>
+        <v>50.89</v>
       </c>
       <c r="K120" s="13" t="n">
-        <v>61.3</v>
+        <v>50.94</v>
       </c>
       <c r="L120" s="13" t="n">
-        <v>69.02</v>
+        <v>62.81</v>
       </c>
       <c r="M120" s="13" t="n">
-        <v>0</v>
+        <v>72.86</v>
       </c>
       <c r="N120" s="13" t="n">
         <v>0</v>
@@ -9522,27 +9861,30 @@
         <v>0</v>
       </c>
       <c r="P120" s="13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q120" s="13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="R120" s="13" t="n">
-        <v>43.79</v>
+        <v>0</v>
       </c>
       <c r="S120" s="13" t="n">
-        <v>53.85</v>
+        <v>43.6</v>
       </c>
       <c r="T120" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" s="14">
-        <f>F120*T120/100</f>
-        <v/>
-      </c>
-      <c r="V120" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>56.4</v>
+      </c>
+      <c r="U120" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="14">
+        <f>F120*U120/100</f>
+        <v/>
+      </c>
+      <c r="W120" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -9574,26 +9916,26 @@
         <v>11.059</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>641522</v>
+        <v>641534</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>9438064</v>
-      </c>
-      <c r="I121" s="8" t="n">
-        <v>48.25</v>
+        <v>9438065</v>
+      </c>
+      <c r="I121" s="6" t="n">
+        <v>11.059</v>
       </c>
       <c r="J121" s="8" t="n">
-        <v>48.07</v>
+        <v>50.33</v>
       </c>
       <c r="K121" s="8" t="n">
-        <v>62.54</v>
+        <v>52.44</v>
       </c>
       <c r="L121" s="8" t="n">
+        <v>64.04000000000001</v>
+      </c>
+      <c r="M121" s="8" t="n">
         <v>77.04000000000001</v>
       </c>
-      <c r="M121" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="N121" s="8" t="n">
         <v>0</v>
       </c>
@@ -9601,27 +9943,30 @@
         <v>0</v>
       </c>
       <c r="P121" s="8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q121" s="8" t="n">
-        <v>4.13</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R121" s="8" t="n">
-        <v>49.59</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S121" s="8" t="n">
-        <v>43.8</v>
+        <v>45.53</v>
       </c>
       <c r="T121" s="8" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="U121" s="9">
-        <f>F121*T121/100</f>
-        <v/>
-      </c>
-      <c r="V121" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>52.03</v>
+      </c>
+      <c r="U121" s="8" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="V121" s="9">
+        <f>F121*U121/100</f>
+        <v/>
+      </c>
+      <c r="W121" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -9653,26 +9998,26 @@
         <v>0.859</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>642690</v>
+        <v>642692</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>9438409</v>
-      </c>
-      <c r="I122" s="13" t="n">
-        <v>54.8</v>
+        <v>9438414</v>
+      </c>
+      <c r="I122" s="11" t="n">
+        <v>0.859</v>
       </c>
       <c r="J122" s="13" t="n">
-        <v>53.98</v>
+        <v>54.32</v>
       </c>
       <c r="K122" s="13" t="n">
+        <v>53.12</v>
+      </c>
+      <c r="L122" s="13" t="n">
         <v>64.45999999999999</v>
       </c>
-      <c r="L122" s="13" t="n">
+      <c r="M122" s="13" t="n">
         <v>64.51000000000001</v>
       </c>
-      <c r="M122" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="N122" s="13" t="n">
         <v>0</v>
       </c>
@@ -9686,21 +10031,24 @@
         <v>0</v>
       </c>
       <c r="R122" s="13" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="S122" s="13" t="n">
-        <v>66.67</v>
+        <v>28.57</v>
       </c>
       <c r="T122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" s="14">
-        <f>F122*T122/100</f>
-        <v/>
-      </c>
-      <c r="V122" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="U122" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="14">
+        <f>F122*U122/100</f>
+        <v/>
+      </c>
+      <c r="W122" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -9732,25 +10080,25 @@
         <v>90.197</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>636249</v>
+        <v>636261</v>
       </c>
       <c r="H123" s="7" t="n">
-        <v>9425665</v>
-      </c>
-      <c r="I123" s="8" t="n">
-        <v>41.15</v>
+        <v>9425725</v>
+      </c>
+      <c r="I123" s="6" t="n">
+        <v>90.197</v>
       </c>
       <c r="J123" s="8" t="n">
-        <v>41.66</v>
+        <v>39.76</v>
       </c>
       <c r="K123" s="8" t="n">
-        <v>57.51</v>
+        <v>40.78</v>
       </c>
       <c r="L123" s="8" t="n">
-        <v>72.31</v>
+        <v>55.17</v>
       </c>
       <c r="M123" s="8" t="n">
-        <v>0</v>
+        <v>71.52</v>
       </c>
       <c r="N123" s="8" t="n">
         <v>0</v>
@@ -9759,27 +10107,30 @@
         <v>0.2</v>
       </c>
       <c r="P123" s="8" t="n">
-        <v>2.09</v>
+        <v>0.5</v>
       </c>
       <c r="Q123" s="8" t="n">
-        <v>7.37</v>
+        <v>2.98</v>
       </c>
       <c r="R123" s="8" t="n">
-        <v>66.73</v>
+        <v>9.33</v>
       </c>
       <c r="S123" s="8" t="n">
-        <v>23.61</v>
+        <v>65.64</v>
       </c>
       <c r="T123" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" s="9">
-        <f>F123*T123/100</f>
-        <v/>
-      </c>
-      <c r="V123" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>21.35</v>
+      </c>
+      <c r="U123" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="9">
+        <f>F123*U123/100</f>
+        <v/>
+      </c>
+      <c r="W123" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -9811,54 +10162,57 @@
         <v>58.292</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>634061</v>
+        <v>634041</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>9426778</v>
-      </c>
-      <c r="I124" s="13" t="n">
-        <v>40.07</v>
+        <v>9426830</v>
+      </c>
+      <c r="I124" s="11" t="n">
+        <v>58.292</v>
       </c>
       <c r="J124" s="13" t="n">
-        <v>40.73</v>
+        <v>43.06</v>
       </c>
       <c r="K124" s="13" t="n">
-        <v>56.96</v>
+        <v>42.93</v>
       </c>
       <c r="L124" s="13" t="n">
+        <v>57.83</v>
+      </c>
+      <c r="M124" s="13" t="n">
         <v>71.68000000000001</v>
       </c>
-      <c r="M124" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="N124" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O124" s="13" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="P124" s="13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q124" s="13" t="n">
-        <v>10.85</v>
+        <v>0.63</v>
       </c>
       <c r="R124" s="13" t="n">
-        <v>64.03</v>
+        <v>6.26</v>
       </c>
       <c r="S124" s="13" t="n">
-        <v>21.71</v>
+        <v>67.14</v>
       </c>
       <c r="T124" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" s="14">
-        <f>F124*T124/100</f>
-        <v/>
-      </c>
-      <c r="V124" s="10" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>25.98</v>
+      </c>
+      <c r="U124" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" s="14">
+        <f>F124*U124/100</f>
+        <v/>
+      </c>
+      <c r="W124" s="10" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -9890,54 +10244,57 @@
         <v>283.428</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>626078</v>
+        <v>626122</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>9427110</v>
-      </c>
-      <c r="I125" s="8" t="n">
-        <v>24.78</v>
+        <v>9427151</v>
+      </c>
+      <c r="I125" s="6" t="n">
+        <v>283.428</v>
       </c>
       <c r="J125" s="8" t="n">
-        <v>18.08</v>
+        <v>24.92</v>
       </c>
       <c r="K125" s="8" t="n">
-        <v>50.81</v>
+        <v>19.37</v>
       </c>
       <c r="L125" s="8" t="n">
-        <v>111.24</v>
+        <v>48.41</v>
       </c>
       <c r="M125" s="8" t="n">
-        <v>0.1</v>
+        <v>75</v>
       </c>
       <c r="N125" s="8" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="O125" s="8" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="P125" s="8" t="n">
-        <v>31.31</v>
+        <v>0.03</v>
       </c>
       <c r="Q125" s="8" t="n">
-        <v>35.69</v>
+        <v>29.78</v>
       </c>
       <c r="R125" s="8" t="n">
-        <v>21.02</v>
+        <v>34.41</v>
       </c>
       <c r="S125" s="8" t="n">
-        <v>9.300000000000001</v>
+        <v>27.17</v>
       </c>
       <c r="T125" s="8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U125" s="9">
-        <f>F125*T125/100</f>
-        <v/>
-      </c>
-      <c r="V125" s="5" t="inlineStr">
-        <is>
-          <t>Círculo de área equivalente</t>
+        <v>8.6</v>
+      </c>
+      <c r="U125" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" s="9">
+        <f>F125*U125/100</f>
+        <v/>
+      </c>
+      <c r="W125" s="5" t="inlineStr">
+        <is>
+          <t>Polígono del bloque</t>
         </is>
       </c>
     </row>
@@ -9957,11 +10314,14 @@
       </c>
       <c r="G126" s="15" t="n"/>
       <c r="H126" s="15" t="n"/>
-      <c r="I126" s="17">
-        <f>SUMPRODUCT(F9:F125,I9:I125)/F126</f>
-        <v/>
-      </c>
-      <c r="J126" s="15" t="n"/>
+      <c r="I126" s="16">
+        <f>SUM(I9:I125)</f>
+        <v/>
+      </c>
+      <c r="J126" s="17">
+        <f>SUMPRODUCT(F9:F125,J9:J125)/F126</f>
+        <v/>
+      </c>
       <c r="K126" s="15" t="n"/>
       <c r="L126" s="15" t="n"/>
       <c r="M126" s="15" t="n"/>
@@ -9972,11 +10332,12 @@
       <c r="R126" s="15" t="n"/>
       <c r="S126" s="15" t="n"/>
       <c r="T126" s="15" t="n"/>
-      <c r="U126" s="18">
-        <f>SUM(U9:U125)</f>
-        <v/>
-      </c>
-      <c r="V126" s="15" t="n"/>
+      <c r="U126" s="15" t="n"/>
+      <c r="V126" s="18">
+        <f>SUM(V9:V125)</f>
+        <v/>
+      </c>
+      <c r="W126" s="15" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="19" t="inlineStr">
@@ -9986,14 +10347,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:V125"/>
+  <autoFilter ref="A8:W125"/>
   <mergeCells count="6">
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="A5:V5"/>
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A6:V6"/>
-    <mergeCell ref="A3:V3"/>
-    <mergeCell ref="A4:V4"/>
+    <mergeCell ref="A5:W5"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A6:W6"/>
+    <mergeCell ref="A4:W4"/>
+    <mergeCell ref="A3:W3"/>
+    <mergeCell ref="A2:W2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -10055,7 +10416,7 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Fuente: DEM: Copernicus GLO-30 (ESA, 30 m, modelo de superficie). Bloques: catálogo V6 (datos/unidades_liberacion_areas.csv).</t>
+          <t>Fuente: DEM: Copernicus GLO-30 (ESA, 30 m, modelo de superficie). Bloques: capa Bloques V6 (datos/bloques_v6.gpkg) y catálogo V6.</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10472,7 @@
         <v/>
       </c>
       <c r="E9" s="9">
-        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B9,'Pendientes por bloque'!$U$9:$U$125)</f>
+        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B9,'Pendientes por bloque'!$V$9:$V$125)</f>
         <v/>
       </c>
       <c r="F9" s="8">
@@ -10139,7 +10500,7 @@
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B10,'Pendientes por bloque'!$U$9:$U$125)</f>
+        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B10,'Pendientes por bloque'!$V$9:$V$125)</f>
         <v/>
       </c>
       <c r="F10" s="13">
@@ -10167,7 +10528,7 @@
         <v/>
       </c>
       <c r="E11" s="9">
-        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B11,'Pendientes por bloque'!$U$9:$U$125)</f>
+        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B11,'Pendientes por bloque'!$V$9:$V$125)</f>
         <v/>
       </c>
       <c r="F11" s="8">
@@ -10195,7 +10556,7 @@
         <v/>
       </c>
       <c r="E12" s="14">
-        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B12,'Pendientes por bloque'!$U$9:$U$125)</f>
+        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B12,'Pendientes por bloque'!$V$9:$V$125)</f>
         <v/>
       </c>
       <c r="F12" s="13">
@@ -10223,7 +10584,7 @@
         <v/>
       </c>
       <c r="E13" s="9">
-        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B13,'Pendientes por bloque'!$U$9:$U$125)</f>
+        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B13,'Pendientes por bloque'!$V$9:$V$125)</f>
         <v/>
       </c>
       <c r="F13" s="8">
@@ -10251,7 +10612,7 @@
         <v/>
       </c>
       <c r="E14" s="14">
-        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B14,'Pendientes por bloque'!$U$9:$U$125)</f>
+        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B14,'Pendientes por bloque'!$V$9:$V$125)</f>
         <v/>
       </c>
       <c r="F14" s="13">
@@ -10279,7 +10640,7 @@
         <v/>
       </c>
       <c r="E15" s="9">
-        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B15,'Pendientes por bloque'!$U$9:$U$125)</f>
+        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B15,'Pendientes por bloque'!$V$9:$V$125)</f>
         <v/>
       </c>
       <c r="F15" s="8">
@@ -10307,7 +10668,7 @@
         <v/>
       </c>
       <c r="E16" s="14">
-        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B16,'Pendientes por bloque'!$U$9:$U$125)</f>
+        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B16,'Pendientes por bloque'!$V$9:$V$125)</f>
         <v/>
       </c>
       <c r="F16" s="13">
@@ -10335,7 +10696,7 @@
         <v/>
       </c>
       <c r="E17" s="9">
-        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B17,'Pendientes por bloque'!$U$9:$U$125)</f>
+        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B17,'Pendientes por bloque'!$V$9:$V$125)</f>
         <v/>
       </c>
       <c r="F17" s="8">
@@ -10363,7 +10724,7 @@
         <v/>
       </c>
       <c r="E18" s="14">
-        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B18,'Pendientes por bloque'!$U$9:$U$125)</f>
+        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B18,'Pendientes por bloque'!$V$9:$V$125)</f>
         <v/>
       </c>
       <c r="F18" s="13">
@@ -10391,7 +10752,7 @@
         <v/>
       </c>
       <c r="E19" s="9">
-        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B19,'Pendientes por bloque'!$U$9:$U$125)</f>
+        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B19,'Pendientes por bloque'!$V$9:$V$125)</f>
         <v/>
       </c>
       <c r="F19" s="8">
@@ -10419,7 +10780,7 @@
         <v/>
       </c>
       <c r="E20" s="14">
-        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B20,'Pendientes por bloque'!$U$9:$U$125)</f>
+        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B20,'Pendientes por bloque'!$V$9:$V$125)</f>
         <v/>
       </c>
       <c r="F20" s="13">
@@ -10447,7 +10808,7 @@
         <v/>
       </c>
       <c r="E21" s="9">
-        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B21,'Pendientes por bloque'!$U$9:$U$125)</f>
+        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B21,'Pendientes por bloque'!$V$9:$V$125)</f>
         <v/>
       </c>
       <c r="F21" s="8">
@@ -10475,7 +10836,7 @@
         <v/>
       </c>
       <c r="E22" s="14">
-        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B22,'Pendientes por bloque'!$U$9:$U$125)</f>
+        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B22,'Pendientes por bloque'!$V$9:$V$125)</f>
         <v/>
       </c>
       <c r="F22" s="13">
@@ -10503,7 +10864,7 @@
         <v/>
       </c>
       <c r="E23" s="9">
-        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B23,'Pendientes por bloque'!$U$9:$U$125)</f>
+        <f>SUMIF('Pendientes por bloque'!$D$9:$D$125,B23,'Pendientes por bloque'!$V$9:$V$125)</f>
         <v/>
       </c>
       <c r="F23" s="8">
@@ -10553,7 +10914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10625,13 +10986,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="75" customHeight="1">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="20" t="n">
         <v>4</v>
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>Ámbito de cálculo: el repositorio no contiene polígonos de los bloques. Cuando la columna 'Ámbito de cálculo' dice 'Círculo de área equivalente', las estadísticas se calcularon sobre un círculo centrado en el centroide del bloque con la misma área del catálogo V6. Son REFERENCIALES. [POR DEFINIR]: recalcular con la capa oficial de polígonos (python mapas_pendientes_v6.py --bloques bloques_v6.gpkg).</t>
+          <t>Ámbito de cálculo: 117 de 117 bloques con su polígono (datos/bloques_v6.gpkg, derivado de la capa 'Bloques V6'); el centroide se toma del polígono.</t>
         </is>
       </c>
     </row>
@@ -10652,6 +11013,26 @@
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t>Control: 117 bloques vigentes del catálogo V6; área total esperada 12,270.235 ha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>Aviso: Bloque 56: el centroide de atributos_bloques_v6.csv (631,723, 9,439,702) está a 16,110 m de su polígono; se usa el del polígono (621,634, 9,452,921)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Aviso: Bloque 57: el centroide de atributos_bloques_v6.csv (631,195, 9,441,777) está a 1,697 m de su polígono; se usa el del polígono (631,727, 9,439,690)</t>
         </is>
       </c>
     </row>
